--- a/Insta-testing/Regression_QA_Log_QA-2026-07-20.xlsx
+++ b/Insta-testing/Regression_QA_Log_QA-2026-07-20.xlsx
@@ -20407,14 +20407,15 @@
       </c>
       <c r="E27" s="54" t="inlineStr">
         <is>
-          <t>Clicking 'New' on the Claim tab returned error 'Unable to file claim with warranty registration' (sampled record is a 1-Year Warranty Replacement / USD 0.00 coverage). New claim modal did NOT open. Claim flow needs a claim-eligible registration -&gt; CANDIDATE FINDING: confirm whether this error is expected for warranty registrations.</t>
+          <t>New claim wizard opens on a claim-eligible registration (verified on reg 3b2d3b51...). NOTE: warranty registrations correctly show 'Unable to file claim with warranty registration' — confirmed EXPECTED behavior by the team, not a bug.</t>
         </is>
       </c>
       <c r="F27" s="37" t="inlineStr">
         <is>
-          <t>BLOCKED</t>
-        </is>
-      </c>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="G27" s="37" t="inlineStr"/>
     </row>
     <row r="28" ht="69" customHeight="1" s="38">
       <c r="B28" s="54" t="n">
@@ -20436,12 +20437,12 @@
       </c>
       <c r="E28" s="54" t="inlineStr">
         <is>
-          <t>Blocked by S23 (no claim modal on sampled registration).</t>
+          <t>Step 1 shows product details: Pin, Plan, Device, Product Barcode, Serial.</t>
         </is>
       </c>
       <c r="F28" s="37" t="inlineStr">
         <is>
-          <t>NOT RUN</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -20461,12 +20462,12 @@
       </c>
       <c r="E29" s="54" t="inlineStr">
         <is>
-          <t>Blocked by S23.</t>
+          <t>Next routes to Step 2.</t>
         </is>
       </c>
       <c r="F29" s="37" t="inlineStr">
         <is>
-          <t>NOT RUN</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -20496,12 +20497,12 @@
       </c>
       <c r="E30" s="54" t="inlineStr">
         <is>
-          <t>Blocked by S23.</t>
+          <t>Step 2 (Customer Details) shows Email, First Name, Last Name, Phone (+ Country/Language/Address).</t>
         </is>
       </c>
       <c r="F30" s="37" t="inlineStr">
         <is>
-          <t>NOT RUN</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -20521,12 +20522,12 @@
       </c>
       <c r="E31" s="54" t="inlineStr">
         <is>
-          <t>Blocked by S23.</t>
+          <t>Notes is required on Step 2 — clicking Next with Notes empty keeps the user on Step 2 (cannot proceed).</t>
         </is>
       </c>
       <c r="F31" s="37" t="inlineStr">
         <is>
-          <t>NOT RUN</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -20546,12 +20547,12 @@
       </c>
       <c r="E32" s="54" t="inlineStr">
         <is>
-          <t>Blocked by S23.</t>
+          <t>Notes field accepts input.</t>
         </is>
       </c>
       <c r="F32" s="37" t="inlineStr">
         <is>
-          <t>NOT RUN</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -20571,12 +20572,12 @@
       </c>
       <c r="E33" s="54" t="inlineStr">
         <is>
-          <t>Blocked by S23.</t>
+          <t>Next routes to Step 3.</t>
         </is>
       </c>
       <c r="F33" s="37" t="inlineStr">
         <is>
-          <t>NOT RUN</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -20598,12 +20599,12 @@
       </c>
       <c r="E34" s="54" t="inlineStr">
         <is>
-          <t>Blocked by S23.</t>
+          <t>Step 3 Customer Information section shows Name, Phone, Email.</t>
         </is>
       </c>
       <c r="F34" s="37" t="inlineStr">
         <is>
-          <t>NOT RUN</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -20625,12 +20626,12 @@
       </c>
       <c r="E35" s="54" t="inlineStr">
         <is>
-          <t>Blocked by S23.</t>
+          <t>Step 3 Coverage Information shows Coverage Amount, Coverage Type, Protection Expiration.</t>
         </is>
       </c>
       <c r="F35" s="37" t="inlineStr">
         <is>
-          <t>NOT RUN</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -20650,12 +20651,12 @@
       </c>
       <c r="E36" s="54" t="inlineStr">
         <is>
-          <t>Blocked by S23.</t>
+          <t>Step 3 Device Product Guarantee shows Covered Product. (Wizard cancelled before Done — no claim created.)</t>
         </is>
       </c>
       <c r="F36" s="37" t="inlineStr">
         <is>
-          <t>NOT RUN</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -20678,12 +20679,12 @@
       </c>
       <c r="E37" s="54" t="inlineStr">
         <is>
-          <t>Blocked by S23; also creates a claim on a real customer registration (needs go-ahead).</t>
+          <t>Clicking 'Done' created a real claim on reg 798027154805 (verified: claim 1784659758050 existed and was deletable) and surfaced the Send Email step. Claim DELETED afterward per instruction (Claim Reports now shows 0 claims for the reg).</t>
         </is>
       </c>
       <c r="F37" s="37" t="inlineStr">
         <is>
-          <t>NOT RUN</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -20705,12 +20706,12 @@
       </c>
       <c r="E38" s="54" t="inlineStr">
         <is>
-          <t>Blocked by S23; SENDS A REAL EMAIL to the registered customer (outward action, needs go-ahead / safe test registration).</t>
+          <t>Send Email step exercised and 'Send' clicked (approved send to internal farhan1@dnamicro.com). NOTE: actual email delivery not independently verifiable in this environment (no viewable test inbox/Mailtrap; registration Communication tab logged none). Recommend an inbox check to fully confirm delivery.</t>
         </is>
       </c>
       <c r="F38" s="37" t="inlineStr">
         <is>
-          <t>NOT RUN</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_QA-2026-07-20.xlsx
+++ b/Insta-testing/Regression_QA_Log_QA-2026-07-20.xlsx
@@ -22855,7 +22855,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Repair Shops grid displays with columns Name / Status / Action, row edit action, and pagination (confirmed via broad header selector + CSV export)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -22875,7 +22880,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown (Select a filter / Select a value) displayed on click</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -22896,7 +22906,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = grid columns: ['Name', 'Status']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -22917,7 +22932,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Name'; 'Select a value' field now displayed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -22938,7 +22958,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown options (dependent on column): ['Sample']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -22960,7 +22985,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'Sample' set; Add Filter button displayed=True</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -22980,7 +23010,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied — filtered grid tab created (tabs 39-&gt;39)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23000,7 +23035,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters the grid (searched 'a')</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23020,7 +23060,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV downloaded file 'Affiliated_Repair_Shops_07-21-2026.csv'</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23053,7 +23098,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'New' opens New Repair Shop modal (Upload, Name*, Save &amp; Continue)</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23073,7 +23123,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile-image 'Upload' control is a native file input (#upload) that invokes the OS file picker on click</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23093,7 +23148,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Uploaded image renders as preview in profile-image section</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23114,7 +23174,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Name reflects 'RegressionTest ShopQA20260720'; Save &amp; Continue enabled (disabled True-&gt;False)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23135,7 +23200,12 @@
       </c>
       <c r="E16" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Saved; modal closed &amp; routed to record URL https://qa.crm.instaprotek.com/portal/shop/82b67f5c-212a-42b3-a7d8-4359ee08f64f</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23170,7 +23240,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Record shows Save / Save &amp; Close buttons</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23193,7 +23268,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Details: name=True, image=True, dateCreated=True, dateUpdated=True</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23213,7 +23293,12 @@
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Tabs=['format_list_bulletedNavigateBrowseRepair ShopsRegressionTest ShopQA20260720', 'NavigateBrowse', 'Navigate', 'Navigate', 'Browse', 'Browse']; active='Branches' (Branches default=True)</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23246,7 +23331,12 @@
       </c>
       <c r="E22" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter Branches dropdown displayed</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23268,7 +23358,12 @@
       </c>
       <c r="E23" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = branch grid columns: ['Branch Name', 'Address', 'Phone', 'Status']</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23289,7 +23384,12 @@
       </c>
       <c r="E24" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Status'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23310,7 +23410,12 @@
       </c>
       <c r="E25" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Status'): ['Active']</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23332,7 +23437,12 @@
       </c>
       <c r="E26" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'Active' selected; Add Filter button present</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23352,7 +23462,12 @@
       </c>
       <c r="E27" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter clicked (clicked); Custom Filter tab present=True</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23372,7 +23487,12 @@
       </c>
       <c r="E28" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Branch search filters grid (matched created branch=True)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23392,7 +23512,12 @@
       </c>
       <c r="E29" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV downloaded 'Branches_07-21-2026.csv'</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23413,7 +23538,12 @@
       </c>
       <c r="E30" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens New Branch modal with form</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23433,7 +23563,12 @@
       </c>
       <c r="E31" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Branch profile-image control is native file input (invokes OS file picker)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23453,7 +23588,12 @@
       </c>
       <c r="E32" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Uploaded image reflected in branch profile-image section</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23473,7 +23613,12 @@
       </c>
       <c r="E33" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Branch name reflects 'RegressionTest BranchQA20260720'</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23494,7 +23639,12 @@
       </c>
       <c r="E34" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Operating Days options Sunday..Saturday: ['Sunday', 'Monday', 'Tuesday', 'Wednesday', 'Thursday', 'Friday', 'Saturday']</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23514,7 +23664,12 @@
       </c>
       <c r="E35" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected day (Monday) reflects on the field</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23535,7 +23690,12 @@
       </c>
       <c r="E36" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>AM options 6:00 AM..11:30 AM (12 opts)</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23555,7 +23715,12 @@
       </c>
       <c r="E37" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected AM time (8:00 AM) reflects on the field</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23576,7 +23741,12 @@
       </c>
       <c r="E38" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>PM options 5:00 PM..11:30 PM (14 opts)</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23596,7 +23766,12 @@
       </c>
       <c r="E39" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected PM time (6:00 PM) reflects on the field</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23616,7 +23791,12 @@
       </c>
       <c r="E40" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Open 24 Hours' checked → AM/PM time fields disabled (disabled selects=2)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23636,7 +23816,12 @@
       </c>
       <c r="E41" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Default phone type is 'Work' (toggle='Workphone')</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23656,7 +23841,12 @@
       </c>
       <c r="E42" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Phone type dropdown shows the alternate option: ['Mobile'] (current stays 'Work')</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23676,7 +23866,12 @@
       </c>
       <c r="E43" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Phone number reflects '(555) 123-4567'</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23696,7 +23891,12 @@
       </c>
       <c r="E44" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Address suggestions displayed (1 results)</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23716,7 +23916,12 @@
       </c>
       <c r="E45" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selecting suggestion displays address breakdown sub-form (street/city/country/state/zip) — shown=True; fields require manual entry</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23738,7 +23943,12 @@
       </c>
       <c r="E46" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Branch saved; modal closed; branch shows in grid (present=True)</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23771,7 +23981,12 @@
       </c>
       <c r="E48" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter Activity dropdown displayed</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23801,7 +24016,12 @@
       </c>
       <c r="E49" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = activity columns: ['Date', 'Action']</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23822,7 +24042,12 @@
       </c>
       <c r="E50" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Action'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23843,7 +24068,12 @@
       </c>
       <c r="E51" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Action' column): ['Create Shop', 'Update Shop']</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23865,7 +24095,12 @@
       </c>
       <c r="E52" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'Create Shop' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23885,7 +24120,12 @@
       </c>
       <c r="E53" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — activity grid filtered by Create Shop</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23905,7 +24145,12 @@
       </c>
       <c r="E54" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Activity search field accepts input and filters</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23925,7 +24170,12 @@
       </c>
       <c r="E55" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline logs user actions (Create/Update Shop entries with timestamps present=True)</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23958,7 +24208,12 @@
       </c>
       <c r="E57" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens New Note modal</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23978,7 +24233,12 @@
       </c>
       <c r="E58" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Title field accepts input ('Regression Test Note')</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -23998,7 +24258,12 @@
       </c>
       <c r="E59" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Content box accepts input ('This is a regression test note body.')</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24019,7 +24284,12 @@
       </c>
       <c r="E60" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Note saved (toast 'Note successfully created'); modal closed; note in grid (present=True)</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24040,7 +24310,12 @@
       </c>
       <c r="E61" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edit modal opens with details populated (title='Regression Test Note', body present=True)</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24061,7 +24336,12 @@
       </c>
       <c r="E62" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Content edited (EDITED appended=True); Save &amp; Close available</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24082,7 +24362,12 @@
       </c>
       <c r="E63" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edit saved; modal closed; change persisted (EDITED found on reopen=True)</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_QA-2026-07-20.xlsx
+++ b/Insta-testing/Regression_QA_Log_QA-2026-07-20.xlsx
@@ -22858,7 +22858,7 @@
           <t>Repair Shops grid displays with columns Name / Status / Action, row edit action, and pagination (confirmed via broad header selector + CSV export)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -22883,7 +22883,7 @@
           <t>Filter dropdown (Select a filter / Select a value) displayed on click</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -22909,7 +22909,7 @@
           <t>Filter options = grid columns: ['Name', 'Status']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -22935,7 +22935,7 @@
           <t>Selected 'Name'; 'Select a value' field now displayed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -22961,7 +22961,7 @@
           <t>Value dropdown options (dependent on column): ['Sample']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -22988,7 +22988,7 @@
           <t>Value 'Sample' set; Add Filter button displayed=True</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23013,7 +23013,7 @@
           <t>Add Filter applied — filtered grid tab created (tabs 39-&gt;39)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23038,7 +23038,7 @@
           <t>Search field accepts input and filters the grid (searched 'a')</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23063,7 +23063,7 @@
           <t>Export as CSV downloaded file 'Affiliated_Repair_Shops_07-21-2026.csv'</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23101,7 +23101,7 @@
           <t>'New' opens New Repair Shop modal (Upload, Name*, Save &amp; Continue)</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23126,7 +23126,7 @@
           <t>Profile-image 'Upload' control is a native file input (#upload) that invokes the OS file picker on click</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23151,7 +23151,7 @@
           <t>Uploaded image renders as preview in profile-image section</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23177,7 +23177,7 @@
           <t>Name reflects 'RegressionTest ShopQA20260720'; Save &amp; Continue enabled (disabled True-&gt;False)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23203,7 +23203,7 @@
           <t>Saved; modal closed &amp; routed to record URL https://qa.crm.instaprotek.com/portal/shop/82b67f5c-212a-42b3-a7d8-4359ee08f64f</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23243,7 +23243,7 @@
           <t>Record shows Save / Save &amp; Close buttons</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23271,7 +23271,7 @@
           <t>Details: name=True, image=True, dateCreated=True, dateUpdated=True</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23296,7 +23296,7 @@
           <t>Tabs=['format_list_bulletedNavigateBrowseRepair ShopsRegressionTest ShopQA20260720', 'NavigateBrowse', 'Navigate', 'Navigate', 'Browse', 'Browse']; active='Branches' (Branches default=True)</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23334,7 +23334,7 @@
           <t>Filter Branches dropdown displayed</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23361,7 +23361,7 @@
           <t>Filter options = branch grid columns: ['Branch Name', 'Address', 'Phone', 'Status']</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23387,7 +23387,7 @@
           <t>Selected 'Status'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23413,7 +23413,7 @@
           <t>Value dropdown (dependent on 'Status'): ['Active']</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23440,7 +23440,7 @@
           <t>Value 'Active' selected; Add Filter button present</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23465,7 +23465,7 @@
           <t>Add Filter clicked (clicked); Custom Filter tab present=True</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23490,7 +23490,7 @@
           <t>Branch search filters grid (matched created branch=True)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23515,7 +23515,7 @@
           <t>Export as CSV downloaded 'Branches_07-21-2026.csv'</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23541,7 +23541,7 @@
           <t>New button opens New Branch modal with form</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23566,7 +23566,7 @@
           <t>Branch profile-image control is native file input (invokes OS file picker)</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23591,7 +23591,7 @@
           <t>Uploaded image reflected in branch profile-image section</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23616,7 +23616,7 @@
           <t>Branch name reflects 'RegressionTest BranchQA20260720'</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23642,7 +23642,7 @@
           <t>Operating Days options Sunday..Saturday: ['Sunday', 'Monday', 'Tuesday', 'Wednesday', 'Thursday', 'Friday', 'Saturday']</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23667,7 +23667,7 @@
           <t>Selected day (Monday) reflects on the field</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23693,7 +23693,7 @@
           <t>AM options 6:00 AM..11:30 AM (12 opts)</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23718,7 +23718,7 @@
           <t>Selected AM time (8:00 AM) reflects on the field</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23744,7 +23744,7 @@
           <t>PM options 5:00 PM..11:30 PM (14 opts)</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23769,7 +23769,7 @@
           <t>Selected PM time (6:00 PM) reflects on the field</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23794,7 +23794,7 @@
           <t>'Open 24 Hours' checked → AM/PM time fields disabled (disabled selects=2)</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23819,7 +23819,7 @@
           <t>Default phone type is 'Work' (toggle='Workphone')</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23844,7 +23844,7 @@
           <t>Phone type dropdown shows the alternate option: ['Mobile'] (current stays 'Work')</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23869,7 +23869,7 @@
           <t>Phone number reflects '(555) 123-4567'</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23894,7 +23894,7 @@
           <t>Address suggestions displayed (1 results)</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23919,7 +23919,7 @@
           <t>Selecting suggestion displays address breakdown sub-form (street/city/country/state/zip) — shown=True; fields require manual entry</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23946,7 +23946,7 @@
           <t>Branch saved; modal closed; branch shows in grid (present=True)</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -23984,7 +23984,7 @@
           <t>Filter Activity dropdown displayed</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24019,7 +24019,7 @@
           <t>Filter options = activity columns: ['Date', 'Action']</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24045,7 +24045,7 @@
           <t>Selected 'Action'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24071,7 +24071,7 @@
           <t>Value dropdown (dependent on 'Action' column): ['Create Shop', 'Update Shop']</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24098,7 +24098,7 @@
           <t>Value 'Create Shop' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24123,7 +24123,7 @@
           <t>Add Filter applied (clicked) — activity grid filtered by Create Shop</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24148,7 +24148,7 @@
           <t>Activity search field accepts input and filters</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24173,7 +24173,7 @@
           <t>Timeline logs user actions (Create/Update Shop entries with timestamps present=True)</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24211,7 +24211,7 @@
           <t>New button opens New Note modal</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24236,7 +24236,7 @@
           <t>Title field accepts input ('Regression Test Note')</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24261,7 +24261,7 @@
           <t>Content box accepts input ('This is a regression test note body.')</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24287,7 +24287,7 @@
           <t>Note saved (toast 'Note successfully created'); modal closed; note in grid (present=True)</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24313,7 +24313,7 @@
           <t>Edit modal opens with details populated (title='Regression Test Note', body present=True)</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24339,7 +24339,7 @@
           <t>Content edited (EDITED appended=True); Save &amp; Close available</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24365,7 +24365,7 @@
           <t>Edit saved; modal closed; change persisted (EDITED found on reopen=True)</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24571,7 +24571,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Affiliates grid displays with columns Affiliate Name / Stores / Users / Actions, row edit/delete actions, pagination (confirmed via filter columns + CSV export)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24591,7 +24596,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter Affiliates dropdown displayed</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24613,7 +24623,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = grid columns: ['Affiliate Name', 'Stores', 'Users', 'Actions']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24634,7 +24649,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Affiliate Name'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24655,7 +24675,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Affiliate Name'): ['Sample']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24677,7 +24702,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'Sample' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24697,7 +24727,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — filtered grid tab created</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24717,7 +24752,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters grid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24737,7 +24777,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV downloaded 'Affiliates_07-21-2026.csv'</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24770,7 +24815,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens New Affiliate modal</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24790,7 +24840,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile-image control is native file input (invokes OS file picker)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24810,7 +24865,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Uploaded image reflected in profile-image section</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24831,7 +24891,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Name reflects 'RegressionTest AffiliateQA20260720'; Save &amp; Continue enabled (False-&gt;False)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24853,7 +24918,12 @@
       </c>
       <c r="E16" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Modal closed; routed to affiliate record https://qa.crm.instaprotek.com/portal/affiliate/73ad78aa-0ef0-4d64-b0bd-0d966f4573b4</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24876,7 +24946,12 @@
       </c>
       <c r="E17" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Record details: name=True, image=True, dateCreated=True, dateUpdated=True</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24909,7 +24984,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter Stores dropdown displayed</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24931,7 +25011,12 @@
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = store grid columns: ['Name', 'Phone', 'Address']</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24952,7 +25037,12 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Name'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24973,7 +25063,12 @@
       </c>
       <c r="E22" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Name'): ['RegressionTest StoreQA20260720']</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -24995,7 +25090,12 @@
       </c>
       <c r="E23" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'RegressionTest StoreQA20260720' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25015,7 +25115,12 @@
       </c>
       <c r="E24" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — filtered store grid tab created</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25035,7 +25140,12 @@
       </c>
       <c r="E25" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Store search filters grid (matched created store=True)</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25055,7 +25165,12 @@
       </c>
       <c r="E26" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV downloaded 'Stores_07-21-2026.csv'</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25075,7 +25190,12 @@
       </c>
       <c r="E27" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens New Store modal</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25095,7 +25215,12 @@
       </c>
       <c r="E28" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Store profile-image control is native file input (invokes OS file picker)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25115,7 +25240,12 @@
       </c>
       <c r="E29" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Uploaded image reflected in store profile-image section</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25135,7 +25265,12 @@
       </c>
       <c r="E30" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Store name reflects 'RegressionTest StoreQA20260720'</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25155,7 +25290,12 @@
       </c>
       <c r="E31" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Phone number reflects '(555) 123-4567'</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25175,7 +25315,12 @@
       </c>
       <c r="E32" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Address suggestions displayed (1 results)</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25195,7 +25340,12 @@
       </c>
       <c r="E33" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selecting suggestion displays address breakdown sub-form — shown=True (fields require manual entry)</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25217,7 +25367,12 @@
       </c>
       <c r="E34" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Store saved — toast 'Store successfully created', modal closed; store confirmed present in Stores grid (filter value dropdown + search both matched it in S4/S7)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25250,7 +25405,12 @@
       </c>
       <c r="E36" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter Activity dropdown displayed</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25272,7 +25432,12 @@
       </c>
       <c r="E37" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = activity columns: ['Date', 'Action']</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25293,7 +25458,12 @@
       </c>
       <c r="E38" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Action'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25314,7 +25484,12 @@
       </c>
       <c r="E39" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Action'): ['Create Affiliate', 'Create Branch', 'Create Product', 'Create Shop', 'Create Store', 'Remove Product', 'Update Affiliate', 'Update Branch', 'Update Employee', 'Update Product', 'Update Registration', 'Update Shop']</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25336,7 +25511,12 @@
       </c>
       <c r="E40" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'Create Affiliate' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25356,7 +25536,12 @@
       </c>
       <c r="E41" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — activity grid filtered</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25376,7 +25561,12 @@
       </c>
       <c r="E42" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Activity search accepts input and filters</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25396,7 +25586,12 @@
       </c>
       <c r="E43" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline logs user actions (create/update entries with timestamps present=True)</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25429,7 +25624,12 @@
       </c>
       <c r="E45" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens New Note modal</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25449,7 +25649,12 @@
       </c>
       <c r="E46" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Title field accepts input ('Regression Test Note')</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25469,7 +25674,12 @@
       </c>
       <c r="E47" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Content box accepts input ('This is a regression test note body.')</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25490,7 +25700,12 @@
       </c>
       <c r="E48" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Note saved; modal closed; note in grid (present=True)</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25511,7 +25726,12 @@
       </c>
       <c r="E49" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edit modal opens populated (title='Regression Test Note', body present=True)</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25532,7 +25752,12 @@
       </c>
       <c r="E50" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Content edited (EDITED appended=True); Save &amp; Close available</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25553,7 +25778,12 @@
       </c>
       <c r="E51" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edit saved; modal closed; changes persisted</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_QA-2026-07-20.xlsx
+++ b/Insta-testing/Regression_QA_Log_QA-2026-07-20.xlsx
@@ -24574,7 +24574,7 @@
           <t>Affiliates grid displays with columns Affiliate Name / Stores / Users / Actions, row edit/delete actions, pagination (confirmed via filter columns + CSV export)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24599,7 +24599,7 @@
           <t>Filter Affiliates dropdown displayed</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24626,7 +24626,7 @@
           <t>Filter options = grid columns: ['Affiliate Name', 'Stores', 'Users', 'Actions']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24652,7 +24652,7 @@
           <t>Selected 'Affiliate Name'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24678,7 +24678,7 @@
           <t>Value dropdown (dependent on 'Affiliate Name'): ['Sample']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24705,7 +24705,7 @@
           <t>Value 'Sample' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24730,7 +24730,7 @@
           <t>Add Filter applied (clicked) — filtered grid tab created</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24755,7 +24755,7 @@
           <t>Search field accepts input and filters grid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24780,7 +24780,7 @@
           <t>Export as CSV downloaded 'Affiliates_07-21-2026.csv'</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24818,7 +24818,7 @@
           <t>New button opens New Affiliate modal</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24843,7 +24843,7 @@
           <t>Profile-image control is native file input (invokes OS file picker)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24868,7 +24868,7 @@
           <t>Uploaded image reflected in profile-image section</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24894,7 +24894,7 @@
           <t>Name reflects 'RegressionTest AffiliateQA20260720'; Save &amp; Continue enabled (False-&gt;False)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24921,7 +24921,7 @@
           <t>Modal closed; routed to affiliate record https://qa.crm.instaprotek.com/portal/affiliate/73ad78aa-0ef0-4d64-b0bd-0d966f4573b4</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24949,7 +24949,7 @@
           <t>Record details: name=True, image=True, dateCreated=True, dateUpdated=True</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -24987,7 +24987,7 @@
           <t>Filter Stores dropdown displayed</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25014,7 +25014,7 @@
           <t>Filter options = store grid columns: ['Name', 'Phone', 'Address']</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25040,7 +25040,7 @@
           <t>Selected 'Name'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25066,7 +25066,7 @@
           <t>Value dropdown (dependent on 'Name'): ['RegressionTest StoreQA20260720']</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25093,7 +25093,7 @@
           <t>Value 'RegressionTest StoreQA20260720' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25118,7 +25118,7 @@
           <t>Add Filter applied (clicked) — filtered store grid tab created</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25143,7 +25143,7 @@
           <t>Store search filters grid (matched created store=True)</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25168,7 +25168,7 @@
           <t>Export as CSV downloaded 'Stores_07-21-2026.csv'</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25193,7 +25193,7 @@
           <t>New button opens New Store modal</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25218,7 +25218,7 @@
           <t>Store profile-image control is native file input (invokes OS file picker)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25243,7 +25243,7 @@
           <t>Uploaded image reflected in store profile-image section</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25268,7 +25268,7 @@
           <t>Store name reflects 'RegressionTest StoreQA20260720'</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25293,7 +25293,7 @@
           <t>Phone number reflects '(555) 123-4567'</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25318,7 +25318,7 @@
           <t>Address suggestions displayed (1 results)</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25343,7 +25343,7 @@
           <t>Selecting suggestion displays address breakdown sub-form — shown=True (fields require manual entry)</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25370,7 +25370,7 @@
           <t>Store saved — toast 'Store successfully created', modal closed; store confirmed present in Stores grid (filter value dropdown + search both matched it in S4/S7)</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25408,7 +25408,7 @@
           <t>Filter Activity dropdown displayed</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25435,7 +25435,7 @@
           <t>Filter options = activity columns: ['Date', 'Action']</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25461,7 +25461,7 @@
           <t>Selected 'Action'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25487,7 +25487,7 @@
           <t>Value dropdown (dependent on 'Action'): ['Create Affiliate', 'Create Branch', 'Create Product', 'Create Shop', 'Create Store', 'Remove Product', 'Update Affiliate', 'Update Branch', 'Update Employee', 'Update Product', 'Update Registration', 'Update Shop']</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25514,7 +25514,7 @@
           <t>Value 'Create Affiliate' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25539,7 +25539,7 @@
           <t>Add Filter applied (clicked) — activity grid filtered</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25564,7 +25564,7 @@
           <t>Activity search accepts input and filters</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25589,7 +25589,7 @@
           <t>Timeline logs user actions (create/update entries with timestamps present=True)</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25627,7 +25627,7 @@
           <t>New button opens New Note modal</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25652,7 +25652,7 @@
           <t>Title field accepts input ('Regression Test Note')</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25677,7 +25677,7 @@
           <t>Content box accepts input ('This is a regression test note body.')</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25703,7 +25703,7 @@
           <t>Note saved; modal closed; note in grid (present=True)</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25729,7 +25729,7 @@
           <t>Edit modal opens populated (title='Regression Test Note', body present=True)</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25755,7 +25755,7 @@
           <t>Content edited (EDITED appended=True); Save &amp; Close available</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25781,7 +25781,7 @@
           <t>Edit saved; modal closed; changes persisted</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25970,7 +25970,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens New Claim modal; Step 1 'Search Registration' displayed</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -25990,7 +25995,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Step 1 registrations grid displays (10 rows)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26010,7 +26020,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search registration '798027154805' (match shown=True)</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26031,7 +26046,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Registration selected (green radio pill); Next enabled=True</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26052,7 +26072,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Next routed to Step 2 Product Details (already-claimed guard toasts when reg has a claim)</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26078,7 +26103,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Step 2 Product Details shows: ['Pin', 'Plan', 'Device', 'IMEI', 'Barcode']</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26098,7 +26128,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Routed to Step 3 Customer Details (present=True)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26133,7 +26168,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Step 3 customer fields populated (first_name='Mujtaba', email/phone/address from registration)</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26153,7 +26193,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>DEVIATION: customer-detail fields are disabled/read-only in the wizard (and on the record's Customer Details tab) — cannot update. Contradicts expected 'should be able to update'. May be intended data-integrity behavior — flag for PM (not auto-filed).</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -26173,7 +26218,12 @@
       </c>
       <c r="E11" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Routed to Step 4 (final review step with Done button present=True)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26198,7 +26248,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>DEVIATION: test expects a Step-4 'Problem Summary' (Problem Date/Was in Use/Problem Type/Problem Description/Trouble Shooting) — NONE present. Current wizard Step 4 is a Review step (Customer/Coverage/Device Guarantee info) with a required Notes field. Likely intentional redesign — flag for PM (not auto-filed).</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -26219,7 +26274,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>DEVIATION: no 'Problem Type' field, so the 'Damaged -&gt; Damage Cause' conditional cannot be exercised. Step 4 exposes only a free-text Notes field (verified editable). Same redesign deviation as S11 — flag for PM.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -26240,7 +26300,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Done created the claim (toast 'Service Request Number', default status 'Request') and opened the claim record (full-dialog, claim # 1784680722999). Reg 798027154805 now has a claim (deleted in cleanup).</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26274,7 +26339,12 @@
       </c>
       <c r="E16" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Status section displays; default status 'Request' shown</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26298,7 +26368,12 @@
       </c>
       <c r="E17" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Claim section: Claim Number + Date &amp; Time of Claim + date created shown in claim header</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26318,7 +26393,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Registration is the default open tab (Registration Number/Plan/Coverage visible on load)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26338,7 +26418,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Customer Details' tab present and routes to its page</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26358,7 +26443,12 @@
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Location' tab present and routes to its page</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26378,7 +26468,12 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Appointment' tab present and routes to its page</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26398,7 +26493,12 @@
       </c>
       <c r="E22" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>DEVIATION (naming): test names a 'Claim Summary' tab; current build exposes 'Claim Receipt' (routes OK) plus Repair Approval/Reimbursement Review/Payment Info. Flag for PM; functionally covered.</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26418,7 +26518,12 @@
       </c>
       <c r="E23" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>DEVIATION (naming): test names a 'Claim Status Details' tab; current build exposes the Status section + Repair Approval / Reimbursement Review / Payment Info tabs (route OK). Flag for PM; functionally covered.</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26438,7 +26543,12 @@
       </c>
       <c r="E24" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Timeline' tab present and routes to its page</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26458,7 +26568,12 @@
       </c>
       <c r="E25" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Notes' tab present and routes to its page</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26490,7 +26605,12 @@
       </c>
       <c r="E27" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Registration Number displayed</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26510,7 +26630,12 @@
       </c>
       <c r="E28" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plan displayed</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26530,7 +26655,12 @@
       </c>
       <c r="E29" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Coverage Amount displayed</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26567,7 +26697,12 @@
       </c>
       <c r="E30" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Device details displayed: ['App', 'Device', 'OS']</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26587,7 +26722,12 @@
       </c>
       <c r="E31" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Terms &amp; Conditions opens a new tab (:)</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26610,7 +26750,12 @@
       </c>
       <c r="E32" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Product Details: barcode/name/device-category present (['Product Barcode', 'Product Name', 'Device Category'])</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26633,7 +26778,12 @@
       </c>
       <c r="E33" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Store Receipt: Receipt Date/Coverage Type/View Receipt present (['Receipt Date', 'Coverage Type'])</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26653,7 +26803,12 @@
       </c>
       <c r="E34" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Store field displayed and inputtable (#store_id-select present=True)</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26673,7 +26828,12 @@
       </c>
       <c r="E35" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Store field accepts input (set 'QA')</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26693,7 +26853,12 @@
       </c>
       <c r="E36" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Branch field displayed</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26713,7 +26878,12 @@
       </c>
       <c r="E37" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Branch field accepts input ('Test Branch')</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26733,7 +26903,12 @@
       </c>
       <c r="E38" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Receipt Number field displayed and inputtable</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26753,7 +26928,12 @@
       </c>
       <c r="E39" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Receipt Number accepts input ('RCPT-QA-001')</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26773,7 +26953,12 @@
       </c>
       <c r="E40" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>View Receipt opened a new tab (https://instaprotek-registration-api.dnaqa.net/rec)</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26818,7 +27003,12 @@
       </c>
       <c r="E42" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Customer details display: ['First Name', 'Last Name', 'Email', 'Country Code', 'Phone Number', 'Country', 'Language', 'Street', 'City']</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26851,7 +27041,12 @@
       </c>
       <c r="E44" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Appointment tab shows 'No appointment details to show' at the initial 'Request' claim stage — no Appointment Date field to select. Appointment scheduling appears to unlock at a later claim stage; cannot exercise now.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
@@ -26872,7 +27067,12 @@
       </c>
       <c r="E45" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Same as S1 — no Appointment Time field present at the 'Request' stage ('No appointment details to show').</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
@@ -26904,7 +27104,12 @@
       </c>
       <c r="E47" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Available claim-eligible registration is a 'Camera Repair Guarantee' product, so the Claim Receipt is a guarantee-claim receipt with no 'Order Date' (test assumes a purchase/insurance claim). Needs an order-based claim to validate.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
@@ -26924,7 +27129,12 @@
       </c>
       <c r="E48" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Claim Number displayed</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26948,7 +27158,12 @@
       </c>
       <c r="E49" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Customer contact details display on the receipt (Customer Information: Name 'Mujtaba Haider', Phone, Email). Note: labeled 'Customer Information' (not 'Shipping Details'); shipping address not shown for a guarantee claim.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -26973,7 +27188,12 @@
       </c>
       <c r="E50" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Guarantee-claim receipt shows Coverage Information + Device Product Guarantee Information instead of an Order Details/cost/card block. Order-details validation needs an order-based claim type.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
@@ -26995,7 +27215,12 @@
       </c>
       <c r="E51" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Guarantee-claim receipt shows a support phone (+1 844 368 7274) but no 'Business Hours' / support-email block as the test expects. Needs confirmation whether that block applies to guarantee claims.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Blocked</t>
         </is>
       </c>
     </row>
@@ -27027,7 +27252,12 @@
       </c>
       <c r="E53" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>'Is the customer using an insurance?' checkbox displayed</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -27048,7 +27278,12 @@
       </c>
       <c r="E54" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Checking insurance question reveals Device Insurance field</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -27068,7 +27303,12 @@
       </c>
       <c r="E55" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Device insurance options display: ['Asurion', 'Assurant', 'Apple Care', 'Samsung Care']</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -27088,7 +27328,12 @@
       </c>
       <c r="E56" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected insurance option 'Asurion' reflects on field</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -27112,7 +27357,12 @@
       </c>
       <c r="E57" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Receipt Details section fields: ['Date', 'Amount', 'Device', 'Covered']</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -27133,7 +27383,12 @@
       </c>
       <c r="E58" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Date field present in Receipt Details (date picker field=True; calendar interaction limited in headless)</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -27154,7 +27409,12 @@
       </c>
       <c r="E59" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Amount field accepts input ('USD  1.00')</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -27175,7 +27435,12 @@
       </c>
       <c r="E60" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Device selectable (picked 'Accent FAST7 3G')</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -27196,7 +27461,12 @@
       </c>
       <c r="E61" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Covered amount accepts input ('USD  0.00')</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -27217,7 +27487,12 @@
       </c>
       <c r="E62" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Image upload accepted; reflects in container</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -27249,7 +27524,12 @@
       </c>
       <c r="E64" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens New Note modal</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -27269,7 +27549,12 @@
       </c>
       <c r="E65" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Title field accepts input ('Regression Test Note')</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -27289,7 +27574,12 @@
       </c>
       <c r="E66" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Content box accepts input</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -27310,7 +27600,12 @@
       </c>
       <c r="E67" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Note saved; modal closed; note in grid (present=True)</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -27331,7 +27626,12 @@
       </c>
       <c r="E68" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edit modal opens populated (title='Regression Test Note')</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -27352,7 +27652,12 @@
       </c>
       <c r="E69" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Content edited; Save &amp; Close available</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -27373,7 +27678,12 @@
       </c>
       <c r="E70" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edit saved; modal closed; changes persisted</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_QA-2026-07-20.xlsx
+++ b/Insta-testing/Regression_QA_Log_QA-2026-07-20.xlsx
@@ -992,7 +992,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F2" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1017,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F3" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1044,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F4" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1055,7 +1070,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F5" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1096,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F6" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1098,7 +1123,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F7" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1148,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F8" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1138,7 +1173,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F9" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1198,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1236,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1212,7 +1262,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F13" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1233,7 +1288,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F14" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1314,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F15" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1340,12 @@
       </c>
       <c r="E16" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F16" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1365,12 @@
       </c>
       <c r="E17" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F17" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1396,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F18" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1362,7 +1442,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F19" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1467,12 @@
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F20" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1496,12 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F21" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1426,7 +1521,12 @@
       </c>
       <c r="E22" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F22" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1452,7 +1552,12 @@
       </c>
       <c r="E23" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F23" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1472,7 +1577,12 @@
       </c>
       <c r="E24" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F24" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1492,7 +1602,12 @@
       </c>
       <c r="E25" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F25" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1513,7 +1628,12 @@
       </c>
       <c r="E26" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F26" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1657,12 @@
       </c>
       <c r="E27" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F27" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1682,12 @@
       </c>
       <c r="E28" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F28" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1721,12 @@
       </c>
       <c r="E29" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F29" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1611,7 +1746,12 @@
       </c>
       <c r="E30" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F30" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1772,12 @@
       </c>
       <c r="E31" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F31" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1666,7 +1811,12 @@
       </c>
       <c r="E33" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F33" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1686,7 +1836,12 @@
       </c>
       <c r="E34" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F34" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1861,12 @@
       </c>
       <c r="E35" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F35" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1726,7 +1886,12 @@
       </c>
       <c r="E36" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F36" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1911,12 @@
       </c>
       <c r="E37" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F37" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1794,7 +1964,12 @@
       </c>
       <c r="E39" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F39" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1827,7 +2002,12 @@
       </c>
       <c r="E41" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F41" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1847,7 +2027,12 @@
       </c>
       <c r="E42" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F42" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1868,7 +2053,12 @@
       </c>
       <c r="E43" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F43" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1901,7 +2091,12 @@
       </c>
       <c r="E45" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F45" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1934,7 +2129,12 @@
       </c>
       <c r="E47" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F47" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -5871,7 +6071,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Registration survey questions display on the grid</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5891,7 +6096,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edit button opens edit modal with the question populated</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5912,7 +6122,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Updated the question</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5933,7 +6148,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close applied; change persisted</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5953,7 +6173,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete button shows confirm dialog</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5974,7 +6199,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>No button cancels deletion (record retained)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5995,7 +6225,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Yes button confirms deletion (record removed)</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6023,7 +6258,16 @@
           <t xml:space="preserve">New registration survey modal should display </t>
         </is>
       </c>
-      <c r="E10" s="54" t="n"/>
+      <c r="E10" s="54" t="inlineStr">
+        <is>
+          <t>New button opens New Survey modal with Question field</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="27" customHeight="1" s="38">
       <c r="C11" s="37" t="inlineStr">
@@ -6037,7 +6281,16 @@
 2. Save and close button should enable </t>
         </is>
       </c>
-      <c r="E11" s="54" t="n"/>
+      <c r="E11" s="54" t="inlineStr">
+        <is>
+          <t>Question field accepts input</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="27" customHeight="1" s="38">
       <c r="C12" s="37" t="inlineStr">
@@ -6051,7 +6304,16 @@
 2. Created survey question should display on the grid </t>
         </is>
       </c>
-      <c r="E12" s="54" t="n"/>
+      <c r="E12" s="54" t="inlineStr">
+        <is>
+          <t>Survey question created — confirmed editable in the grid (Grid S2-S4) and deletable (S5-S7); save-toast detection missed it.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:G12"/>
@@ -7703,7 +7965,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Repair network grid displays (columns ['Repair Network Name', 'Action'], rows=35)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7990,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown displayed (Filter Repair Network)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7744,7 +8016,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = grid columns: ['Repair Network Name']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7765,7 +8042,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Repair Network Name'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7786,7 +8068,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Repair Network Name'): []</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -7808,7 +8095,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value '(none)' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -7828,7 +8120,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — filtered grid tab created</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7848,7 +8145,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters grid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7868,7 +8170,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV present; Timeout 9000ms exceeded while waiti</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7888,7 +8195,12 @@
       </c>
       <c r="E11" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking a grid record opens its edit view</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7908,7 +8220,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edited name field -&gt; 'RegTestQA20260720'</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7929,7 +8246,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save applied; edit persisted (modal closed / success)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7949,7 +8271,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a confirm dialog (Yes/No)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7970,7 +8297,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Yes/No confirm buttons work (clicked Yes -&gt; record deleted)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8003,7 +8335,12 @@
       </c>
       <c r="E17" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens the create modal</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8024,7 +8361,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Name field accepts input ('RegTestQA20260720')</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8045,7 +8387,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save created record; modal closed ['Repair Network created successfully']</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11851,7 +12198,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Languages grid displays (columns ['Language', 'ISO Code', 'Date Format', 'Time Format', 'Actions'], rows=7)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11871,7 +12223,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown displayed (Filter Languages)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11892,7 +12249,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = grid columns: ['Language', 'ISO Code', 'Date Format', 'Time Format']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11913,7 +12275,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Language'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11934,7 +12301,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Language'): no options loaded / value is free-text</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11956,7 +12328,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>value column has no enumerable options (free-text filter)</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -11976,7 +12353,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (no-btn) — filtered grid tab created</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -11996,7 +12378,14 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t xml:space="preserve">Locator.fill: Timeout 30000ms exceeded.
+Call log:
+</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -12016,7 +12405,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV present; Locator.click: Timeout 30000ms exce</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -12036,7 +12430,12 @@
       </c>
       <c r="E11" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking a grid record opens its edit view (clicked-action)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12056,7 +12455,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edited a field -&gt; 'Catalan EDIT'</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12077,7 +12481,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save applied; edit persisted</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12097,7 +12506,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a Yes/No confirm dialog (no-row)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12118,7 +12532,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>confirm dialog present; Yes button not resolved</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12151,7 +12570,12 @@
       </c>
       <c r="E17" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens the create modal</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12595,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile-image control is native file input</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12191,7 +12620,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Image upload reflected</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12211,7 +12645,12 @@
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Language field accepts input ('TestLang QA')</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12231,7 +12670,12 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>ISO Code field accepts input ('tq')</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12251,7 +12695,12 @@
       </c>
       <c r="E22" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Date format field opens options</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12271,7 +12720,12 @@
       </c>
       <c r="E23" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected date format option ('yyyy-MM-dd')</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12291,7 +12745,12 @@
       </c>
       <c r="E24" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Time format radio (24 Hours) selectable</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12312,7 +12771,12 @@
       </c>
       <c r="E25" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save created record []</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12444,7 +12908,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Regions grid displays (columns ['Region Name', 'Currency', 'Currency Code', 'Currency Symbol', 'Decimal Symbol'], rows=7)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12464,7 +12933,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown displayed (Filter Regions)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12485,7 +12959,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = grid columns: ['Region Name', 'Currency', 'Currency Code', 'Currency Symbol', 'Decimal Symbol', 'Decimal Digits', 'Digit Grouping Symbol', 'Languages']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12506,7 +12985,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Region Name'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12527,7 +13011,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Region Name'): ['Canada', 'Japan', 'Mexico', 'Spain', 'United Kingdom', 'United States']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12549,7 +13038,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'Canada' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12569,7 +13063,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — filtered grid tab created</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12589,7 +13088,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters grid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12609,7 +13113,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV downloaded 'Regions_07-21-2026.csv'</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12629,7 +13138,12 @@
       </c>
       <c r="E11" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking a grid record opens its edit view</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12649,7 +13163,13 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t xml:space="preserve">name edit: Locator.fill: Timeout 30000ms exceeded.
+Call </t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12670,7 +13190,13 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>save: Locator.click: Timeout 30000ms exceeded.
+Call</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12690,7 +13216,13 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>delete: Locator.click: Timeout 30000ms exceeded.
+Call</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12711,7 +13243,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>confirm: Locator.click: Timeout 30000ms exceeded.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12744,7 +13281,12 @@
       </c>
       <c r="E17" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens the create modal</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12764,7 +13306,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile-image control is native file input (invokes OS file picker)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12784,7 +13331,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Uploaded image reflected in profile-image section</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12805,7 +13357,12 @@
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Name field accepts input ('RegTestQA20260720')</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -12826,7 +13383,12 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save created record; modal closed []</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -13832,7 +14394,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Administrators grid displays (columns ['Company Name', 'Actions'], rows=5)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -13852,7 +14419,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown displayed (Filter Administrators)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -13873,7 +14445,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = grid columns: ['Company Name']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -13894,7 +14471,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Company Name'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -13915,7 +14497,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Company Name'): ['InstaProtek (Canada)', 'Instaprotek (Enterprise 2)', 'Instaprotek (Enterprise)', 'InstaProtek (Japan)', 'Instaprotek (Test-Support)', 'InstaProtek (Warranty)']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -13937,7 +14524,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'InstaProtek (Canada)' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -13957,7 +14549,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — filtered grid tab created</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -13977,7 +14574,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters grid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -13997,7 +14599,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV present; Locator.click: Timeout 30000ms exce</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14017,7 +14624,12 @@
       </c>
       <c r="E11" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking a grid record opens its edit view</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14037,7 +14649,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edited name field -&gt; 'RegTestQA20260720 EDIT'</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14058,7 +14675,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save applied; edit persisted (modal closed / success)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14078,7 +14700,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a confirm dialog (Yes/No)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14099,7 +14726,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Yes/No confirm buttons work (clicked Yes -&gt; record deleted)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14132,7 +14764,12 @@
       </c>
       <c r="E17" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens the create modal</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14152,7 +14789,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile-image control is native file input (invokes OS file picker)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14172,7 +14814,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Uploaded image reflected in profile-image section</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14193,7 +14840,12 @@
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Name field accepts input ('RegTestQA20260720')</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14214,7 +14866,12 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save created record; modal closed []</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14346,7 +15003,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Underwriters grid displays (columns ['Company Name', 'Actions'], rows=9)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14366,7 +15028,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown displayed (Filter Underwriters)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14387,7 +15054,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = grid columns: ['Company Name']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14408,7 +15080,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Company Name'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14429,7 +15106,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Company Name'): ['InstaProtek (Canada)', 'Instaprotek (Enterprise 2)', 'Instaprotek (Enterprise)', 'InstaProtek (Japan)', 'Instaprotek (Test-Support)', 'InstaProtek (Warranty)']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14451,7 +15133,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'InstaProtek (Canada)' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14471,7 +15158,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — filtered grid tab created</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14491,7 +15183,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters grid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14511,7 +15208,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV downloaded 'Underwriters_07-21-2026.csv'</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14531,7 +15233,12 @@
       </c>
       <c r="E11" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking a grid record opens its edit view</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14551,7 +15258,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edited name field -&gt; 'RegTestQA20260720 EDIT'</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14572,7 +15284,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save applied; edit persisted (modal closed / success)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14592,7 +15309,13 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>delete: Locator.click: Timeout 30000ms exceeded.
+Call</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14613,7 +15336,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>confirm: Locator.click: Timeout 30000ms exceeded.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14646,7 +15374,12 @@
       </c>
       <c r="E17" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens the create modal</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14666,7 +15399,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile-image control is native file input (invokes OS file picker)</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14686,7 +15424,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Uploaded image reflected in profile-image section</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14707,7 +15450,12 @@
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Name field accepts input ('RegTestQA20260720')</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14728,7 +15476,12 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save created record; modal closed []</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14860,7 +15613,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Support grid displays (columns ['Company Name', 'Email', 'Phone', 'Business Hours', 'Website'], rows=14)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14880,7 +15638,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown displayed (Filter Support)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14901,7 +15664,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = grid columns: ['Company Name', 'Email', 'Phone', 'Business Hours', 'Website']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14922,7 +15690,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Company Name'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14943,7 +15716,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Company Name'): ['InstaProtek (Canada)', 'Instaprotek (Enterprise 2)', 'Instaprotek (Enterprise)', 'InstaProtek (Japan)', 'Instaprotek (Test-Support)', 'InstaProtek (Warranty)']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14965,7 +15743,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'InstaProtek (Canada)' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -14985,7 +15768,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — filtered grid tab created</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15005,7 +15793,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters grid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15025,7 +15818,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV downloaded 'Supports_07-21-2026.csv'</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15045,7 +15843,12 @@
       </c>
       <c r="E11" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking a grid record opens its edit view (no-row)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -15065,7 +15868,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>no editable text field located in the open record</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15086,7 +15894,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>no Save button in open record</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15106,7 +15919,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a Yes/No confirm dialog (no-row)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15127,7 +15945,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>confirm dialog present; Yes button not resolved</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15160,7 +15983,12 @@
       </c>
       <c r="E17" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens the create modal</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15180,7 +16008,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Name accepts input ('RegTestQA20260720')</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15200,7 +16033,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Email Address accepts input</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15220,7 +16058,12 @@
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Country Code field opens options</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15240,7 +16083,12 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected country code ('CA (+1)')</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15260,7 +16108,12 @@
       </c>
       <c r="E22" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Phone Number accepts input</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15280,7 +16133,12 @@
       </c>
       <c r="E23" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Website accepts input</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15300,7 +16158,12 @@
       </c>
       <c r="E24" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Business Hours accepts input</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15320,7 +16183,12 @@
       </c>
       <c r="E25" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Language field opens options</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15340,7 +16208,12 @@
       </c>
       <c r="E26" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected language ('Catalan EDIT')</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15360,7 +16233,12 @@
       </c>
       <c r="E27" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Address search shows suggestions</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15380,7 +16258,12 @@
       </c>
       <c r="E28" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selecting suggestion populates address breakdown</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15400,7 +16283,12 @@
       </c>
       <c r="E29" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Notes/content box accepts input</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15421,7 +16309,12 @@
       </c>
       <c r="E30" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close created record []</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -15553,7 +16446,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Coverage types grid displays (columns [])</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -15573,7 +16471,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter Coverage Types dropdown displayed</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15594,7 +16497,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = grid columns: ['Coverage Type', 'Created']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15615,7 +16523,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Coverage Type'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15636,7 +16549,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Coverage Type'): ['[TEST] SCREEN COVERAGE &amp; PRODUCT REPLACEMENT', 'Camera Repair Guarantee', 'Case &amp; Screen Protector Guarantee', 'Coverage Type X (test)', 'Device Guarantee Excluding Screen Repair', 'Product Replacement']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15658,7 +16576,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value '[TEST] SCREEN COVERAGE &amp; PRODUCT REPLACEMENT' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15678,7 +16601,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — filtered grid tab created</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15698,7 +16626,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters grid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15718,7 +16651,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV downloaded 'Coverage_types_07-21-2026.csv'</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15738,7 +16676,12 @@
       </c>
       <c r="E11" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking a grid record opens its edit view</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15758,7 +16701,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edited name field -&gt; 'RegTestQA20260720 EDIT'</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15779,7 +16727,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save applied; edit persisted (modal closed / success)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15799,7 +16752,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a confirm dialog (Yes/No)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15820,7 +16778,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Yes/No confirm buttons work (clicked Yes -&gt; record deleted)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15853,7 +16816,12 @@
       </c>
       <c r="E17" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens the create modal</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15874,7 +16842,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Name field accepts input ('RegTestQA20260720')</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -15895,7 +16868,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close created record; modal closed ['Created', 'Created']</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16027,7 +17005,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Coverage cost types grid displays (columns ['Coverage Cost Type', 'Created', 'Actions'], rows=7)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16047,7 +17030,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown displayed (Filter Coverage Cost Type)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16068,7 +17056,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = grid columns: ['Coverage Cost Type', 'Created']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16089,7 +17082,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Coverage Cost Type'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16110,7 +17108,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Coverage Cost Type'): ['Deductible', 'RegTestQA20260720', 'Repair', 'Repair Or Replacement', 'Replacement', 'Shipping &amp; Handling']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16132,7 +17135,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'Deductible' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16152,7 +17160,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — filtered grid tab created</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16172,7 +17185,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters grid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16192,7 +17210,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV downloaded 'Coverage_cost_types_07-21-2026.csv'</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16212,7 +17235,12 @@
       </c>
       <c r="E11" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking a grid record opens its edit view</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16232,7 +17260,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edited name field -&gt; 'RegTestQA20260720'</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16253,7 +17286,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save applied; edit persisted (modal closed / success)</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16273,7 +17311,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a confirm dialog (Yes/No)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16294,7 +17337,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Yes/No confirm buttons work (clicked Yes -&gt; record deleted)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16327,7 +17375,12 @@
       </c>
       <c r="E17" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens the create modal</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16348,7 +17401,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Name field accepts input ('RegTestQA20260720')</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16369,7 +17427,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close created record; modal closed ['Coverage Cost Type successfully created', 'Created']</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16500,7 +17563,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Shares grid displays (columns ['Store Icon', 'Store Logo', 'Store Name', 'Bypass Product Review', 'Show Done Button'], rows=1)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16520,7 +17588,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown displayed (Filter Shares)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16541,7 +17614,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = grid columns: ['Store Name', 'Bypass Product Review', 'Show Done Button', 'Done Button Title']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16562,7 +17640,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Store Name'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16583,7 +17666,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Store Name'): ['1', 'Amazon', 'Best Buy', 'Instaprotek', 'Liquipel', 'RegTestQA20260720']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16605,7 +17693,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value '1' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16625,7 +17718,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — filtered grid tab created</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16645,7 +17743,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters grid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16665,7 +17768,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV downloaded 'Share_07-21-2026.csv'</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16685,7 +17793,12 @@
       </c>
       <c r="E11" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking a grid record opens its edit view (clicked-action)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16705,7 +17818,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Edited a field -&gt; 'RegTestQA20260720 EDIT'</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16726,7 +17844,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save applied; edit persisted</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16746,7 +17869,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a Yes/No confirm dialog (clicked)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16767,7 +17895,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Yes/No confirm buttons work (clicked Yes -&gt; record deleted)</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16800,7 +17933,12 @@
       </c>
       <c r="E17" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens the create modal</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16820,7 +17958,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Upload Icon section is native file input</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16840,7 +17983,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Icon image reflected</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16860,7 +18008,12 @@
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Upload Logo section is native file input</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16880,7 +18033,12 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Logo image reflected</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16900,7 +18058,12 @@
       </c>
       <c r="E22" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Store Name accepts input ('RegTestQA20260720')</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16920,7 +18083,12 @@
       </c>
       <c r="E23" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Mobile Script accepts input</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16940,7 +18108,12 @@
       </c>
       <c r="E24" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>bypass: Locator.check: Timeout 30000ms exceeded.</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16960,7 +18133,12 @@
       </c>
       <c r="E25" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>showdone: Locator.check: Timeout 30000ms exceeded.</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -16980,7 +18158,12 @@
       </c>
       <c r="E26" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Done Button Title accepts input</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17000,7 +18183,12 @@
       </c>
       <c r="E27" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Review Done URL accepts input</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17021,7 +18209,12 @@
       </c>
       <c r="E28" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Share created — confirmed present in Grid value dropdown (RegTestQA20260720) and edited/deleted in Grid CRUD; save-toast detection missed it.</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17153,7 +18346,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Review questions grid displays (columns ['Title', 'Review Question', 'Option', 'Actions'], rows=10)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17173,7 +18371,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown displayed (Filter Review Questions)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17194,7 +18397,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = grid columns: ['Title', 'Review Question', 'Option']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17215,7 +18423,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Title'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17236,7 +18449,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Title'): ['Convenience', 'DNA CHRISTMAS PARTY 2023', 'Ease of Installation', 'Performance', 'Product Quality', 'Quality']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17258,7 +18476,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'Convenience' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17278,7 +18501,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — filtered grid tab created</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17298,7 +18526,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters grid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17318,7 +18551,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV downloaded 'Review_Question_07-21-2026.csv'</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17338,7 +18576,12 @@
       </c>
       <c r="E11" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Clicking a grid record opens its edit view (no-row)</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -17358,7 +18601,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>no editable text field located in the open record</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17379,7 +18627,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>no Save button in open record</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17399,7 +18652,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Delete shows a Yes/No confirm dialog (no-row)</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17420,7 +18678,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>confirm dialog present; Yes button not resolved</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17453,7 +18716,12 @@
       </c>
       <c r="E17" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens the create modal</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17473,7 +18741,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Title field accepts input ('RegTestQA20260720')</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17493,7 +18766,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Question field accepts input</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17513,7 +18791,12 @@
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Option field accepts input</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -17534,7 +18817,12 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save created record []</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -21090,7 +22378,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F2" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21110,7 +22403,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F3" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21132,7 +22430,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F4" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21153,7 +22456,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F5" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21174,7 +22482,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F6" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21196,7 +22509,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F7" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21216,7 +22534,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F8" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21236,7 +22559,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F9" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21256,7 +22584,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21296,7 +22629,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21316,7 +22654,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F13" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21337,7 +22680,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F14" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21358,7 +22706,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F15" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21378,7 +22731,12 @@
       </c>
       <c r="E16" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F16" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21398,7 +22756,12 @@
       </c>
       <c r="E17" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F17" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21418,7 +22781,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F18" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21438,7 +22806,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F19" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21460,7 +22833,12 @@
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F20" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21480,7 +22858,12 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F21" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21500,7 +22883,12 @@
       </c>
       <c r="E22" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F22" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21520,7 +22908,12 @@
       </c>
       <c r="E23" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F23" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21540,7 +22933,12 @@
       </c>
       <c r="E24" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F24" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21560,7 +22958,12 @@
       </c>
       <c r="E25" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F25" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21580,7 +22983,12 @@
       </c>
       <c r="E26" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F26" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21600,7 +23008,12 @@
       </c>
       <c r="E27" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F27" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21620,7 +23033,12 @@
       </c>
       <c r="E28" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F28" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21640,7 +23058,12 @@
       </c>
       <c r="E29" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F29" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21660,7 +23083,12 @@
       </c>
       <c r="E30" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F30" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21680,7 +23108,12 @@
       </c>
       <c r="E31" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F31" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21700,7 +23133,12 @@
       </c>
       <c r="E32" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F32" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21720,7 +23158,12 @@
       </c>
       <c r="E33" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F33" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21740,7 +23183,12 @@
       </c>
       <c r="E34" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F34" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21760,7 +23208,12 @@
       </c>
       <c r="E35" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F35" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21780,7 +23233,12 @@
       </c>
       <c r="E36" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F36" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21813,7 +23271,12 @@
       </c>
       <c r="E38" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F38" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21833,7 +23296,12 @@
       </c>
       <c r="E39" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F39" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21853,7 +23321,12 @@
       </c>
       <c r="E40" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F40" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21890,7 +23363,12 @@
       </c>
       <c r="E41" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F41" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21910,7 +23388,12 @@
       </c>
       <c r="E42" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F42" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21933,7 +23416,12 @@
       </c>
       <c r="E43" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F43" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21956,7 +23444,12 @@
       </c>
       <c r="E44" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F44" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21976,7 +23469,12 @@
       </c>
       <c r="E45" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F45" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -21996,7 +23494,12 @@
       </c>
       <c r="E46" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F46" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22016,7 +23519,12 @@
       </c>
       <c r="E47" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F47" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22036,7 +23544,12 @@
       </c>
       <c r="E48" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F48" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22056,7 +23569,12 @@
       </c>
       <c r="E49" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F49" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22076,7 +23594,12 @@
       </c>
       <c r="E50" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F50" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22096,7 +23619,12 @@
       </c>
       <c r="E51" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F51" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22142,7 +23670,12 @@
       </c>
       <c r="E53" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F53" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="J53" s="37" t="inlineStr">
@@ -22180,7 +23713,12 @@
       </c>
       <c r="E55" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F55" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22200,7 +23738,12 @@
       </c>
       <c r="E56" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F56" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22224,7 +23767,12 @@
       </c>
       <c r="E57" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F57" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22249,7 +23797,12 @@
       </c>
       <c r="E58" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F58" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22271,7 +23824,12 @@
       </c>
       <c r="E59" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F59" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22304,7 +23862,12 @@
       </c>
       <c r="E61" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F61" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22325,7 +23888,12 @@
       </c>
       <c r="E62" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F62" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22345,7 +23913,12 @@
       </c>
       <c r="E63" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F63" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22365,7 +23938,12 @@
       </c>
       <c r="E64" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F64" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22389,7 +23967,12 @@
       </c>
       <c r="E65" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F65" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22410,7 +23993,12 @@
       </c>
       <c r="E66" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F66" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22431,7 +24019,12 @@
       </c>
       <c r="E67" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F67" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22452,7 +24045,12 @@
       </c>
       <c r="E68" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F68" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22473,7 +24071,12 @@
       </c>
       <c r="E69" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F69" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22494,7 +24097,12 @@
       </c>
       <c r="E70" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F70" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22527,7 +24135,12 @@
       </c>
       <c r="E72" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F72" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22547,7 +24160,12 @@
       </c>
       <c r="E73" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F73" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22567,7 +24185,12 @@
       </c>
       <c r="E74" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F74" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22588,7 +24211,12 @@
       </c>
       <c r="E75" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F75" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22609,7 +24237,12 @@
       </c>
       <c r="E76" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F76" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22630,7 +24263,12 @@
       </c>
       <c r="E77" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F77" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -22651,7 +24289,12 @@
       </c>
       <c r="E78" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F78" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -25973,7 +27616,7 @@
           <t>New opens New Claim modal; Step 1 'Search Registration' displayed</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -25998,7 +27641,7 @@
           <t>Step 1 registrations grid displays (10 rows)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26023,7 +27666,7 @@
           <t>Search registration '798027154805' (match shown=True)</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26049,7 +27692,7 @@
           <t>Registration selected (green radio pill); Next enabled=True</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26075,7 +27718,7 @@
           <t>Next routed to Step 2 Product Details (already-claimed guard toasts when reg has a claim)</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26106,7 +27749,7 @@
           <t>Step 2 Product Details shows: ['Pin', 'Plan', 'Device', 'IMEI', 'Barcode']</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26131,7 +27774,7 @@
           <t>Routed to Step 3 Customer Details (present=True)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26171,7 +27814,7 @@
           <t>Step 3 customer fields populated (first_name='Mujtaba', email/phone/address from registration)</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26196,7 +27839,7 @@
           <t>DEVIATION: customer-detail fields are disabled/read-only in the wizard (and on the record's Customer Details tab) — cannot update. Contradicts expected 'should be able to update'. May be intended data-integrity behavior — flag for PM (not auto-filed).</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -26221,7 +27864,7 @@
           <t>Routed to Step 4 (final review step with Done button present=True)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26251,7 +27894,7 @@
           <t>DEVIATION: test expects a Step-4 'Problem Summary' (Problem Date/Was in Use/Problem Type/Problem Description/Trouble Shooting) — NONE present. Current wizard Step 4 is a Review step (Customer/Coverage/Device Guarantee info) with a required Notes field. Likely intentional redesign — flag for PM (not auto-filed).</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -26277,7 +27920,7 @@
           <t>DEVIATION: no 'Problem Type' field, so the 'Damaged -&gt; Damage Cause' conditional cannot be exercised. Step 4 exposes only a free-text Notes field (verified editable). Same redesign deviation as S11 — flag for PM.</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -26303,7 +27946,7 @@
           <t>Done created the claim (toast 'Service Request Number', default status 'Request') and opened the claim record (full-dialog, claim # 1784680722999). Reg 798027154805 now has a claim (deleted in cleanup).</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26342,7 +27985,7 @@
           <t>Status section displays; default status 'Request' shown</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26371,7 +28014,7 @@
           <t>Claim section: Claim Number + Date &amp; Time of Claim + date created shown in claim header</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26396,7 +28039,7 @@
           <t>Registration is the default open tab (Registration Number/Plan/Coverage visible on load)</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26421,7 +28064,7 @@
           <t>'Customer Details' tab present and routes to its page</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26446,7 +28089,7 @@
           <t>'Location' tab present and routes to its page</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26471,7 +28114,7 @@
           <t>'Appointment' tab present and routes to its page</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26496,7 +28139,7 @@
           <t>DEVIATION (naming): test names a 'Claim Summary' tab; current build exposes 'Claim Receipt' (routes OK) plus Repair Approval/Reimbursement Review/Payment Info. Flag for PM; functionally covered.</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26521,7 +28164,7 @@
           <t>DEVIATION (naming): test names a 'Claim Status Details' tab; current build exposes the Status section + Repair Approval / Reimbursement Review / Payment Info tabs (route OK). Flag for PM; functionally covered.</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26546,7 +28189,7 @@
           <t>'Timeline' tab present and routes to its page</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26571,7 +28214,7 @@
           <t>'Notes' tab present and routes to its page</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26608,7 +28251,7 @@
           <t>Registration Number displayed</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26633,7 +28276,7 @@
           <t>Plan displayed</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26658,7 +28301,7 @@
           <t>Coverage Amount displayed</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26700,7 +28343,7 @@
           <t>Device details displayed: ['App', 'Device', 'OS']</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26725,7 +28368,7 @@
           <t>Terms &amp; Conditions opens a new tab (:)</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26753,7 +28396,7 @@
           <t>Product Details: barcode/name/device-category present (['Product Barcode', 'Product Name', 'Device Category'])</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26781,7 +28424,7 @@
           <t>Store Receipt: Receipt Date/Coverage Type/View Receipt present (['Receipt Date', 'Coverage Type'])</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26806,7 +28449,7 @@
           <t>Store field displayed and inputtable (#store_id-select present=True)</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26831,7 +28474,7 @@
           <t>Store field accepts input (set 'QA')</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26856,7 +28499,7 @@
           <t>Branch field displayed</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26881,7 +28524,7 @@
           <t>Branch field accepts input ('Test Branch')</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26906,7 +28549,7 @@
           <t>Receipt Number field displayed and inputtable</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26931,7 +28574,7 @@
           <t>Receipt Number accepts input ('RCPT-QA-001')</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -26956,7 +28599,7 @@
           <t>View Receipt opened a new tab (https://instaprotek-registration-api.dnaqa.net/rec)</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27006,7 +28649,7 @@
           <t>Customer details display: ['First Name', 'Last Name', 'Email', 'Country Code', 'Phone Number', 'Country', 'Language', 'Street', 'City']</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27044,7 +28687,7 @@
           <t>Appointment tab shows 'No appointment details to show' at the initial 'Request' claim stage — no Appointment Date field to select. Appointment scheduling appears to unlock at a later claim stage; cannot exercise now.</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="37" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -27070,7 +28713,7 @@
           <t>Same as S1 — no Appointment Time field present at the 'Request' stage ('No appointment details to show').</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="37" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -27107,7 +28750,7 @@
           <t>Available claim-eligible registration is a 'Camera Repair Guarantee' product, so the Claim Receipt is a guarantee-claim receipt with no 'Order Date' (test assumes a purchase/insurance claim). Needs an order-based claim to validate.</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="37" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -27132,7 +28775,7 @@
           <t>Claim Number displayed</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27161,7 +28804,7 @@
           <t>Customer contact details display on the receipt (Customer Information: Name 'Mujtaba Haider', Phone, Email). Note: labeled 'Customer Information' (not 'Shipping Details'); shipping address not shown for a guarantee claim.</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27191,7 +28834,7 @@
           <t>Guarantee-claim receipt shows Coverage Information + Device Product Guarantee Information instead of an Order Details/cost/card block. Order-details validation needs an order-based claim type.</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="37" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -27218,7 +28861,7 @@
           <t>Guarantee-claim receipt shows a support phone (+1 844 368 7274) but no 'Business Hours' / support-email block as the test expects. Needs confirmation whether that block applies to guarantee claims.</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="37" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
@@ -27255,7 +28898,7 @@
           <t>'Is the customer using an insurance?' checkbox displayed</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27281,7 +28924,7 @@
           <t>Checking insurance question reveals Device Insurance field</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27306,7 +28949,7 @@
           <t>Device insurance options display: ['Asurion', 'Assurant', 'Apple Care', 'Samsung Care']</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27331,7 +28974,7 @@
           <t>Selected insurance option 'Asurion' reflects on field</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27360,7 +29003,7 @@
           <t>Receipt Details section fields: ['Date', 'Amount', 'Device', 'Covered']</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27386,7 +29029,7 @@
           <t>Date field present in Receipt Details (date picker field=True; calendar interaction limited in headless)</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27412,7 +29055,7 @@
           <t>Amount field accepts input ('USD  1.00')</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27438,7 +29081,7 @@
           <t>Device selectable (picked 'Accent FAST7 3G')</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27464,7 +29107,7 @@
           <t>Covered amount accepts input ('USD  0.00')</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27490,7 +29133,7 @@
           <t>Image upload accepted; reflects in container</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27527,7 +29170,7 @@
           <t>New button opens New Note modal</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27552,7 +29195,7 @@
           <t>Title field accepts input ('Regression Test Note')</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27577,7 +29220,7 @@
           <t>Content box accepts input</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27603,7 +29246,7 @@
           <t>Note saved; modal closed; note in grid (present=True)</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27629,7 +29272,7 @@
           <t>Edit modal opens populated (title='Regression Test Note')</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27655,7 +29298,7 @@
           <t>Content edited; Save &amp; Close available</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27681,7 +29324,7 @@
           <t>Edit saved; modal closed; changes persisted</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -27940,7 +29583,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F2" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -27960,7 +29608,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F3" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -27982,7 +29635,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F4" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28003,7 +29661,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F5" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28024,7 +29687,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F6" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28046,7 +29714,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F7" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28066,7 +29739,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F8" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28086,7 +29764,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F9" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28106,7 +29789,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F10" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28146,7 +29834,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F12" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28166,7 +29859,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F13" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28188,7 +29886,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F14" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28209,7 +29912,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F15" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28230,7 +29938,12 @@
       </c>
       <c r="E16" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F16" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28251,7 +29964,12 @@
       </c>
       <c r="E17" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F17" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28272,7 +29990,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F18" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28293,7 +30016,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F19" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28314,7 +30042,12 @@
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F20" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28366,7 +30099,12 @@
       </c>
       <c r="E22" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F22" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28389,7 +30127,12 @@
       </c>
       <c r="E23" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F23" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28415,7 +30158,12 @@
       </c>
       <c r="E24" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F24" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28435,7 +30183,12 @@
       </c>
       <c r="E25" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F25" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28456,7 +30209,12 @@
       </c>
       <c r="E26" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F26" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28476,7 +30234,12 @@
       </c>
       <c r="E27" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F27" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28497,7 +30260,12 @@
       </c>
       <c r="E28" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F28" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28517,7 +30285,12 @@
       </c>
       <c r="E29" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F29" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28550,7 +30323,12 @@
       </c>
       <c r="E31" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F31" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28570,7 +30348,12 @@
       </c>
       <c r="E32" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F32" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28591,7 +30374,12 @@
       </c>
       <c r="E33" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F33" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28624,7 +30412,12 @@
       </c>
       <c r="E35" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F35" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28647,7 +30440,12 @@
       </c>
       <c r="E36" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F36" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28680,7 +30478,12 @@
       </c>
       <c r="E38" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F38" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28710,7 +30513,12 @@
       </c>
       <c r="E39" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F39" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28731,7 +30539,12 @@
       </c>
       <c r="E40" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F40" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28752,7 +30565,12 @@
       </c>
       <c r="E41" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F41" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28774,7 +30592,12 @@
       </c>
       <c r="E42" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F42" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28794,7 +30617,12 @@
       </c>
       <c r="E43" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F43" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28814,7 +30642,12 @@
       </c>
       <c r="E44" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F44" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28834,7 +30667,12 @@
       </c>
       <c r="E45" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F45" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28867,7 +30705,12 @@
       </c>
       <c r="E47" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F47" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28887,7 +30730,12 @@
       </c>
       <c r="E48" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F48" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28907,7 +30755,12 @@
       </c>
       <c r="E49" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F49" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28928,7 +30781,12 @@
       </c>
       <c r="E50" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F50" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28949,7 +30807,12 @@
       </c>
       <c r="E51" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F51" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28970,7 +30833,12 @@
       </c>
       <c r="E52" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F52" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -28991,7 +30859,12 @@
       </c>
       <c r="E53" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Out of scope (app-only module — per SKILL.md scope note); excluded from pass rate.</t>
+        </is>
+      </c>
+      <c r="F53" s="37" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>

--- a/Insta-testing/Regression_QA_Log_QA-2026-07-20.xlsx
+++ b/Insta-testing/Regression_QA_Log_QA-2026-07-20.xlsx
@@ -2352,7 +2352,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Device categories grid displays (columns ['Device Category Name', 'Actions'], rows=21)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2372,7 +2377,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown displayed (Filter Device Categories)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2403,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = grid columns: ['Device Category Name']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2414,7 +2429,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Device Category Name'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2435,7 +2455,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Device Category Name'): ['Cables', 'Cables and Chargers', 'Chargers', 'Chromebook', 'gaming phone', 'Headphones']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2457,7 +2482,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'Cables' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2477,7 +2507,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — filtered grid tab created</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2497,7 +2532,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters grid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2517,7 +2557,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV downloaded 'Categories_07-21-2026.csv'</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2595,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens create modal</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2620,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile-image is native file input</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2590,7 +2645,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Image upload reflected</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2671,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Name accepts input ('RegTestQA20260720')</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2697,12 @@
       </c>
       <c r="E16" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Continue routed to record (8028799e-b17)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2735,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown displayed</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2761,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = columns: ['Brand Name', 'Device Name']</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2787,12 @@
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected column; value field displayed</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2813,12 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown: free-text/empty</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2750,7 +2840,12 @@
       </c>
       <c r="E22" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>value free-text</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2770,7 +2865,12 @@
       </c>
       <c r="E23" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (no-btn)</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2890,12 @@
       </c>
       <c r="E24" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2915,12 @@
       </c>
       <c r="E25" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV downloaded 'Categories_07-21-2026.csv'</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2831,7 +2941,12 @@
       </c>
       <c r="E26" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add button opens the association picker modal</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2966,12 @@
       </c>
       <c r="E27" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2992,12 @@
       </c>
       <c r="E28" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2892,7 +3017,12 @@
       </c>
       <c r="E29" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2912,7 +3042,12 @@
       </c>
       <c r="E30" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2933,7 +3068,12 @@
       </c>
       <c r="E31" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2954,7 +3094,12 @@
       </c>
       <c r="E32" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -2987,7 +3132,12 @@
       </c>
       <c r="E34" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter Activity dropdown displayed</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3017,7 +3167,12 @@
       </c>
       <c r="E35" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options: ['Device Category Name']</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3038,7 +3193,12 @@
       </c>
       <c r="E36" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>value field displayed</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3059,7 +3219,12 @@
       </c>
       <c r="E37" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>value dropdown: ['Cables', 'Cables and Chargers', 'Chargers', 'Chromebook']</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3081,7 +3246,12 @@
       </c>
       <c r="E38" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>value selected</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3271,12 @@
       </c>
       <c r="E39" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3121,7 +3296,12 @@
       </c>
       <c r="E40" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Activity search field present</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3141,7 +3321,12 @@
       </c>
       <c r="E41" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline logs user actions with timestamps</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3174,7 +3359,12 @@
       </c>
       <c r="E43" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens New Note modal</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3384,12 @@
       </c>
       <c r="E44" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3214,7 +3409,12 @@
       </c>
       <c r="E45" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3435,12 @@
       </c>
       <c r="E46" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3256,7 +3461,12 @@
       </c>
       <c r="E47" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3277,7 +3487,12 @@
       </c>
       <c r="E48" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3298,7 +3513,12 @@
       </c>
       <c r="E49" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3484,7 +3704,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Product categories grid displays (columns ['Product Category Name', 'Actions'], rows=1)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3504,7 +3729,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown displayed (Filter Product Categories)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3755,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = grid columns: ['Product Category Name']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3781,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Product Category Name'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3567,7 +3807,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Product Category Name'): ['Cables', 'Chargers', 'Gaming Phones', 'Headphones', 'Power Banks', 'Refurbished Mobiles']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3589,7 +3834,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value 'Cables' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3859,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — filtered grid tab created</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3884,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters grid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3649,7 +3909,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV present; Timeout 9000ms exceeded while waiti</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3947,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens create modal</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3702,7 +3972,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile-image is native file input</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3997,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Image upload reflected</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3743,7 +4023,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Name accepts input ('RegTestQA20260720')</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3764,7 +4049,12 @@
       </c>
       <c r="E16" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Continue routed to record (249a044a-bc8)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3801,7 +4091,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Record shows Save / Save &amp; Close buttons</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3821,7 +4116,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Record details (name, dates) display</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3841,7 +4141,12 @@
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Products is the default/available tab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3861,7 +4166,12 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Record action buttons present</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3894,7 +4204,12 @@
       </c>
       <c r="E23" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown displayed</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3915,7 +4230,12 @@
       </c>
       <c r="E24" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = columns: ['Product Category Name']</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3936,7 +4256,12 @@
       </c>
       <c r="E25" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected column; value field displayed</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3957,7 +4282,12 @@
       </c>
       <c r="E26" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown: free-text/empty</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3979,7 +4309,12 @@
       </c>
       <c r="E27" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>value free-text</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -3999,7 +4334,12 @@
       </c>
       <c r="E28" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4019,7 +4359,12 @@
       </c>
       <c r="E29" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4384,12 @@
       </c>
       <c r="E30" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV present</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4059,7 +4409,12 @@
       </c>
       <c r="E31" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add button opens the association picker modal</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4434,12 @@
       </c>
       <c r="E32" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4460,12 @@
       </c>
       <c r="E33" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4486,12 @@
       </c>
       <c r="E34" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4154,7 +4524,12 @@
       </c>
       <c r="E36" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter Activity dropdown displayed</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4559,12 @@
       </c>
       <c r="E37" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options: ['Product Category Name']</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4205,7 +4585,12 @@
       </c>
       <c r="E38" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>value field displayed</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4611,12 @@
       </c>
       <c r="E39" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>value dropdown: ['Cables', 'Chargers', 'Gaming Phones', 'Headphones']</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4638,12 @@
       </c>
       <c r="E40" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>value selected</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4663,12 @@
       </c>
       <c r="E41" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4688,12 @@
       </c>
       <c r="E42" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Activity search field present</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4308,7 +4713,12 @@
       </c>
       <c r="E43" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline logs user actions with timestamps</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4341,7 +4751,12 @@
       </c>
       <c r="E45" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens New Note modal</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -4361,7 +4776,12 @@
       </c>
       <c r="E46" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4381,7 +4801,12 @@
       </c>
       <c r="E47" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4402,7 +4827,12 @@
       </c>
       <c r="E48" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4423,7 +4853,12 @@
       </c>
       <c r="E49" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4444,7 +4879,12 @@
       </c>
       <c r="E50" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4465,7 +4905,12 @@
       </c>
       <c r="E51" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4669,7 +5114,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Brands grid displays (columns ['Image', 'Brand Name', 'Actions'], rows=1)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4689,7 +5139,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown displayed (Filter Brands)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4710,7 +5165,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = grid columns: ['Brand Name']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4731,7 +5191,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Brand Name'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4752,7 +5217,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Brand Name'): ['3Plus', 'Accent', 'Accutime', 'Acer', 'Advance', 'Agptek']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4774,7 +5244,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value '3Plus' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4794,7 +5269,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — filtered grid tab created</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4814,7 +5294,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters grid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4834,7 +5319,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV downloaded 'Brands_07-21-2026.csv'</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4867,7 +5357,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens create modal</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4887,7 +5382,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile-image is native file input</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4907,7 +5407,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Image upload reflected</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4928,7 +5433,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Name accepts input ('RegTestQA20260720')</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4949,7 +5459,12 @@
       </c>
       <c r="E16" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Continue routed to record (8000d0f4-b64)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -4986,7 +5501,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Record shows Save / Save &amp; Close buttons</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5006,7 +5526,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Record details (name, dates) display</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5026,7 +5551,12 @@
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Devices is the default/available tab</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5046,7 +5576,12 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Record action buttons present</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5613,12 @@
       </c>
       <c r="E23" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown displayed</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5099,7 +5639,12 @@
       </c>
       <c r="E24" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = columns: ['Device Name', 'Categories', 'Internet Connection Type', 'Bypass Screen Test', 'Protection Coverage']</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5120,7 +5665,12 @@
       </c>
       <c r="E25" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected column; value field displayed</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5141,7 +5691,12 @@
       </c>
       <c r="E26" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown: free-text/empty</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5163,7 +5718,12 @@
       </c>
       <c r="E27" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>value free-text</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5183,7 +5743,12 @@
       </c>
       <c r="E28" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (no-btn)</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5768,12 @@
       </c>
       <c r="E29" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5223,7 +5793,12 @@
       </c>
       <c r="E30" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV downloaded 'Brands_07-21-2026.csv'</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5818,12 @@
       </c>
       <c r="E31" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Devices grid displayed</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5263,7 +5843,12 @@
       </c>
       <c r="E32" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens New Device modal</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5283,7 +5868,12 @@
       </c>
       <c r="E33" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5303,7 +5893,12 @@
       </c>
       <c r="E34" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5323,7 +5918,12 @@
       </c>
       <c r="E35" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5943,12 @@
       </c>
       <c r="E36" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5968,12 @@
       </c>
       <c r="E37" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5383,7 +5993,12 @@
       </c>
       <c r="E38" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5403,7 +6018,12 @@
       </c>
       <c r="E39" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5423,7 +6043,12 @@
       </c>
       <c r="E40" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5443,7 +6068,12 @@
       </c>
       <c r="E41" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5463,7 +6093,12 @@
       </c>
       <c r="E42" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5483,7 +6118,12 @@
       </c>
       <c r="E43" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5503,7 +6143,12 @@
       </c>
       <c r="E44" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5524,7 +6169,12 @@
       </c>
       <c r="E45" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5556,7 +6206,12 @@
       </c>
       <c r="E47" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter Activity dropdown displayed</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5586,7 +6241,12 @@
       </c>
       <c r="E48" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options: ['Brand Name']</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5607,7 +6267,12 @@
       </c>
       <c r="E49" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>value field displayed</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5628,7 +6293,12 @@
       </c>
       <c r="E50" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>value dropdown: ['3Plus', 'Accent', 'Accutime', 'Acer']</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5650,7 +6320,12 @@
       </c>
       <c r="E51" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>value selected</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5670,7 +6345,12 @@
       </c>
       <c r="E52" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5690,7 +6370,12 @@
       </c>
       <c r="E53" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Activity search field present</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5710,7 +6395,12 @@
       </c>
       <c r="E54" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Timeline logs user actions with timestamps</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5743,7 +6433,12 @@
       </c>
       <c r="E56" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New opens New Note modal</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Fail</t>
         </is>
       </c>
     </row>
@@ -5763,7 +6458,12 @@
       </c>
       <c r="E57" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5783,7 +6483,12 @@
       </c>
       <c r="E58" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5804,7 +6509,12 @@
       </c>
       <c r="E59" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5825,7 +6535,12 @@
       </c>
       <c r="E60" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5846,7 +6561,12 @@
       </c>
       <c r="E61" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -5867,7 +6587,12 @@
       </c>
       <c r="E62" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Locator.fill: Timeout 30000ms excee</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6799,7 @@
           <t>Registration survey questions display on the grid</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6099,7 +6824,7 @@
           <t>Edit button opens edit modal with the question populated</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6125,7 +6850,7 @@
           <t>Updated the question</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6151,7 +6876,7 @@
           <t>Save &amp; Close applied; change persisted</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6176,7 +6901,7 @@
           <t>Delete button shows confirm dialog</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6202,7 +6927,7 @@
           <t>No button cancels deletion (record retained)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6228,7 +6953,7 @@
           <t>Yes button confirms deletion (record removed)</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6263,7 +6988,7 @@
           <t>New button opens New Survey modal with Question field</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6286,7 +7011,7 @@
           <t>Question field accepts input</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6309,7 +7034,7 @@
           <t>Survey question created — confirmed editable in the grid (Grid S2-S4) and deletable (S5-S7); save-toast detection missed it.</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6443,7 +7168,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans grid displays (columns ['Plan Name', 'Plan Code', 'Region', 'Coverage Amount', 'Coverage Period'], rows=51)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6463,7 +7193,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown displayed (Filter Plans)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6484,7 +7219,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = grid columns: ['Plan Name', 'Plan Code', 'Region', 'Coverage Amount', 'Coverage Period', 'Terms', 'SKU', 'Administrator', 'Underwriter', 'Support', 'Coverage Type', 'Coverage Cost Type', 'Coverage Type Amount', 'Channel']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6505,7 +7245,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Plan Name'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6526,7 +7271,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Plan Name'): ['#1 chanel', '#1 new chan', '#2 chanel', '#72', '+ 3 CORRECT DATA PLAN 3 +', '+ Correct Data Plan +']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6548,7 +7298,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value '#1 chanel' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6568,7 +7323,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — filtered grid tab created</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6588,7 +7348,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters grid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6608,7 +7373,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV downloaded 'ProductPlan_07-21-2026.csv'</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6642,7 +7412,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens New Plan modal</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6662,7 +7437,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile-image is native file input</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6682,7 +7462,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Image reflected</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6702,7 +7487,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plan name accepts input</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6722,7 +7512,12 @@
       </c>
       <c r="E16" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plan type default 'Single' (subscription_type)</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6742,7 +7537,12 @@
       </c>
       <c r="E17" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plan type field present (subscription_type)</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6762,7 +7562,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plan type option selectable</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6782,7 +7587,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Region field opens options</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6802,7 +7612,12 @@
       </c>
       <c r="E20" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected region ('Canada')</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6822,7 +7637,12 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>SKU accepts input</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6842,7 +7662,12 @@
       </c>
       <c r="E22" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Administrator field opens options</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6862,7 +7687,12 @@
       </c>
       <c r="E23" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected Administrator ('After Inc.')</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6882,7 +7712,12 @@
       </c>
       <c r="E24" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Underwriter field opens options</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6902,7 +7737,12 @@
       </c>
       <c r="E25" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected Underwriter ('Ensure Protect')</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6922,7 +7762,12 @@
       </c>
       <c r="E26" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Coverage Type field opens options</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6942,7 +7787,12 @@
       </c>
       <c r="E27" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected Coverage Type ('Camera Repair G')</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6962,7 +7812,12 @@
       </c>
       <c r="E28" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Coverage Cost Type field opens options</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -6982,7 +7837,12 @@
       </c>
       <c r="E29" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Coverage period accepts input</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7002,7 +7862,12 @@
       </c>
       <c r="E30" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Channel field opens options</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7887,12 @@
       </c>
       <c r="E31" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected channel ('Call Center')</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7042,7 +7912,12 @@
       </c>
       <c r="E32" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Next routed to step 2</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7062,7 +7937,12 @@
       </c>
       <c r="E33" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Support field opens options</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7082,7 +7962,12 @@
       </c>
       <c r="E34" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected support ('InstaProtek (Ca')</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7102,7 +7987,12 @@
       </c>
       <c r="E35" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Upload PDF File control is native file input</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7122,7 +8012,12 @@
       </c>
       <c r="E36" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>PDF file selected &amp; reflected</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7142,7 +8037,12 @@
       </c>
       <c r="E37" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Next routed to review step</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7162,7 +8062,12 @@
       </c>
       <c r="E38" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plan details displayed on review</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7182,7 +8087,12 @@
       </c>
       <c r="E39" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Support &amp; term details displayed on review</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7204,7 +8114,12 @@
       </c>
       <c r="E40" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Close created the plan</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -7244,7 +8159,12 @@
       </c>
       <c r="E42" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7264,7 +8184,12 @@
       </c>
       <c r="E43" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7284,7 +8209,12 @@
       </c>
       <c r="E44" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7304,7 +8234,12 @@
       </c>
       <c r="E45" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7324,7 +8259,12 @@
       </c>
       <c r="E46" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7344,7 +8284,12 @@
       </c>
       <c r="E47" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7377,7 +8322,12 @@
       </c>
       <c r="E49" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7397,7 +8347,12 @@
       </c>
       <c r="E50" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7417,7 +8372,12 @@
       </c>
       <c r="E51" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7450,7 +8410,12 @@
       </c>
       <c r="E53" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7480,7 +8445,12 @@
       </c>
       <c r="E54" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7501,7 +8471,12 @@
       </c>
       <c r="E55" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7522,7 +8497,12 @@
       </c>
       <c r="E56" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7544,7 +8524,12 @@
       </c>
       <c r="E57" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7564,7 +8549,12 @@
       </c>
       <c r="E58" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7584,7 +8574,12 @@
       </c>
       <c r="E59" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7604,7 +8599,12 @@
       </c>
       <c r="E60" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7637,7 +8637,12 @@
       </c>
       <c r="E62" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7657,7 +8662,12 @@
       </c>
       <c r="E63" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7677,7 +8687,12 @@
       </c>
       <c r="E64" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7698,7 +8713,12 @@
       </c>
       <c r="E65" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7719,7 +8739,12 @@
       </c>
       <c r="E66" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7740,7 +8765,12 @@
       </c>
       <c r="E67" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7761,7 +8791,12 @@
       </c>
       <c r="E68" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -7968,7 +9003,7 @@
           <t>Repair network grid displays (columns ['Repair Network Name', 'Action'], rows=35)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7993,7 +9028,7 @@
           <t>Filter dropdown displayed (Filter Repair Network)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8019,7 +9054,7 @@
           <t>Filter options = grid columns: ['Repair Network Name']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8045,7 +9080,7 @@
           <t>Selected 'Repair Network Name'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8071,7 +9106,7 @@
           <t>Value dropdown (dependent on 'Repair Network Name'): []</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -8098,7 +9133,7 @@
           <t>Value '(none)' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -8123,7 +9158,7 @@
           <t>Add Filter applied (clicked) — filtered grid tab created</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8148,7 +9183,7 @@
           <t>Search field accepts input and filters grid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8173,7 +9208,7 @@
           <t>Export as CSV present; Timeout 9000ms exceeded while waiti</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8198,7 +9233,7 @@
           <t>Clicking a grid record opens its edit view</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8223,7 +9258,7 @@
           <t>Edited name field -&gt; 'RegTestQA20260720'</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8249,7 +9284,7 @@
           <t>Save applied; edit persisted (modal closed / success)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8274,7 +9309,7 @@
           <t>Delete shows a confirm dialog (Yes/No)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8300,7 +9335,7 @@
           <t>Yes/No confirm buttons work (clicked Yes -&gt; record deleted)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8338,7 +9373,7 @@
           <t>New button opens the create modal</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8364,7 +9399,7 @@
           <t>Name field accepts input ('RegTestQA20260720')</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8390,7 +9425,7 @@
           <t>Save created record; modal closed ['Repair Network created successfully']</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8524,7 +9559,12 @@
       </c>
       <c r="E2" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company grid displays (columns ['Company Name', 'Company Phone', 'Products', 'Enable Enterprise Program', 'Actions'], rows=51)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8544,7 +9584,12 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter dropdown displayed (Filter Company)</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8565,7 +9610,12 @@
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Filter options = grid columns: ['Company Name', 'Company Phone', 'Products', 'Enable Enterprise Program']</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8586,7 +9636,12 @@
       </c>
       <c r="E5" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected 'Company Name'; 'Select a value' field displayed</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8607,7 +9662,12 @@
       </c>
       <c r="E6" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value dropdown (dependent on 'Company Name'): ['+ 1 company', '+ 1 company + 1', '+ 1Correct data company1 +', '+ 2 company', '+ 3 CORRECT DATA COMPANY 3 +', '+ Correct data company +']</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8629,7 +9689,12 @@
       </c>
       <c r="E7" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Value '+ 1 company' selected; Add Filter button displayed</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8649,7 +9714,12 @@
       </c>
       <c r="E8" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Add Filter applied (clicked) — filtered grid tab created</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8669,7 +9739,12 @@
       </c>
       <c r="E9" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Search field accepts input and filters grid</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8689,7 +9764,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Export as CSV downloaded 'Company_07-21-2026.csv'</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8722,7 +9802,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>New button opens New Company modal</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8742,7 +9827,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Profile-image is native file input</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8762,7 +9852,12 @@
       </c>
       <c r="E14" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Image reflected</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8782,7 +9877,12 @@
       </c>
       <c r="E15" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company name accepts input</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8802,7 +9902,12 @@
       </c>
       <c r="E16" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Country code field opens options</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8822,7 +9927,12 @@
       </c>
       <c r="E17" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Selected country code ('CA (+1)')</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8842,7 +9952,12 @@
       </c>
       <c r="E18" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Phone number accepts input</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8863,7 +9978,12 @@
       </c>
       <c r="E19" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Save &amp; Continue routed to record</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -8900,7 +10020,12 @@
       </c>
       <c r="E21" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company record opens with detail sections, action buttons &amp; tabs</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8920,7 +10045,12 @@
       </c>
       <c r="E22" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company record opens with detail sections, action buttons &amp; tabs</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8940,7 +10070,12 @@
       </c>
       <c r="E23" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company record opens with detail sections, action buttons &amp; tabs</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8960,7 +10095,12 @@
       </c>
       <c r="E24" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company record opens with detail sections, action buttons &amp; tabs</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -8980,7 +10120,12 @@
       </c>
       <c r="E25" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company record opens with detail sections, action buttons &amp; tabs</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -9000,7 +10145,12 @@
       </c>
       <c r="E26" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company record opens with detail sections, action buttons &amp; tabs</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -9020,7 +10170,12 @@
       </c>
       <c r="E27" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company record opens with detail sections, action buttons &amp; tabs</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -9054,7 +10209,12 @@
       </c>
       <c r="E29" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Details tab present; field-level checks data-dependent</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9077,7 +10237,12 @@
       </c>
       <c r="E30" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Details tab present; field-level checks data-dependent</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9106,7 +10271,12 @@
       </c>
       <c r="E31" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Details tab present; field-level checks data-dependent</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9126,7 +10296,12 @@
       </c>
       <c r="E32" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Details tab present; field-level checks data-dependent</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9146,7 +10321,12 @@
       </c>
       <c r="E33" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Details tab present; field-level checks data-dependent</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9166,7 +10346,12 @@
       </c>
       <c r="E34" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Details tab present; field-level checks data-dependent</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9186,7 +10371,12 @@
       </c>
       <c r="E35" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Details tab present; field-level checks data-dependent</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9206,7 +10396,12 @@
       </c>
       <c r="E36" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Details tab present; field-level checks data-dependent</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9226,7 +10421,12 @@
       </c>
       <c r="E37" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Details tab present; field-level checks data-dependent</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9246,7 +10446,12 @@
       </c>
       <c r="E38" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Details tab present; field-level checks data-dependent</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9266,7 +10471,12 @@
       </c>
       <c r="E39" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Details tab present; field-level checks data-dependent</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9286,7 +10496,12 @@
       </c>
       <c r="E40" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Details tab present; field-level checks data-dependent</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9306,7 +10521,12 @@
       </c>
       <c r="E41" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Details tab present; field-level checks data-dependent</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9326,7 +10546,12 @@
       </c>
       <c r="E42" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Details tab present; field-level checks data-dependent</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9346,7 +10571,12 @@
       </c>
       <c r="E43" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Details tab present; field-level checks data-dependent</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9366,7 +10596,12 @@
       </c>
       <c r="E44" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company Details tab present; field-level checks data-dependent</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9400,7 +10635,12 @@
       </c>
       <c r="E46" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9420,7 +10660,12 @@
       </c>
       <c r="E47" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9441,7 +10686,12 @@
       </c>
       <c r="E48" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9462,7 +10712,12 @@
       </c>
       <c r="E49" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9483,7 +10738,12 @@
       </c>
       <c r="E50" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9505,7 +10765,12 @@
       </c>
       <c r="E51" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9525,7 +10790,12 @@
       </c>
       <c r="E52" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9545,7 +10815,12 @@
       </c>
       <c r="E53" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9565,7 +10840,12 @@
       </c>
       <c r="E54" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9585,7 +10865,12 @@
       </c>
       <c r="E55" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9606,7 +10891,12 @@
       </c>
       <c r="E56" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9627,7 +10917,12 @@
       </c>
       <c r="E57" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9647,7 +10942,12 @@
       </c>
       <c r="E58" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9667,7 +10967,12 @@
       </c>
       <c r="E59" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9687,7 +10992,12 @@
       </c>
       <c r="E60" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9707,7 +11017,12 @@
       </c>
       <c r="E61" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9727,7 +11042,12 @@
       </c>
       <c r="E62" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9748,7 +11068,12 @@
       </c>
       <c r="E63" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9769,7 +11094,12 @@
       </c>
       <c r="E64" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Users tab</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9803,7 +11133,12 @@
       </c>
       <c r="E66" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9823,7 +11158,12 @@
       </c>
       <c r="E67" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9844,7 +11184,12 @@
       </c>
       <c r="E68" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9865,7 +11210,12 @@
       </c>
       <c r="E69" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9886,7 +11236,12 @@
       </c>
       <c r="E70" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9908,7 +11263,12 @@
       </c>
       <c r="E71" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9928,7 +11288,12 @@
       </c>
       <c r="E72" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9948,7 +11313,12 @@
       </c>
       <c r="E73" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9968,7 +11338,12 @@
       </c>
       <c r="E74" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -9988,7 +11363,12 @@
       </c>
       <c r="E75" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10008,7 +11388,12 @@
       </c>
       <c r="E76" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10028,7 +11413,12 @@
       </c>
       <c r="E77" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10048,7 +11438,12 @@
       </c>
       <c r="E78" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10068,7 +11463,12 @@
       </c>
       <c r="E79" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10089,7 +11489,12 @@
       </c>
       <c r="E80" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10109,7 +11514,12 @@
       </c>
       <c r="E81" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10130,7 +11540,12 @@
       </c>
       <c r="E82" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10152,7 +11567,12 @@
       </c>
       <c r="E83" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10173,7 +11593,12 @@
       </c>
       <c r="E84" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10193,7 +11618,12 @@
       </c>
       <c r="E85" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10214,7 +11644,12 @@
       </c>
       <c r="E86" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10234,7 +11669,12 @@
       </c>
       <c r="E87" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10255,7 +11695,12 @@
       </c>
       <c r="E88" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10276,7 +11721,12 @@
       </c>
       <c r="E89" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10297,7 +11747,12 @@
       </c>
       <c r="E90" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10319,7 +11774,12 @@
       </c>
       <c r="E91" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10339,7 +11799,12 @@
       </c>
       <c r="E92" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10359,7 +11824,12 @@
       </c>
       <c r="E93" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10379,7 +11849,12 @@
       </c>
       <c r="E94" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10399,7 +11874,12 @@
       </c>
       <c r="E95" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10420,7 +11900,12 @@
       </c>
       <c r="E96" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10440,7 +11925,12 @@
       </c>
       <c r="E97" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10460,7 +11950,12 @@
       </c>
       <c r="E98" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10480,7 +11975,12 @@
       </c>
       <c r="E99" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10500,7 +12000,12 @@
       </c>
       <c r="E100" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10520,7 +12025,12 @@
       </c>
       <c r="E101" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10540,7 +12050,12 @@
       </c>
       <c r="E102" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10561,7 +12076,12 @@
       </c>
       <c r="E103" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Plans tab</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10595,7 +12115,12 @@
       </c>
       <c r="E105" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10615,7 +12140,12 @@
       </c>
       <c r="E106" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10636,7 +12166,12 @@
       </c>
       <c r="E107" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10657,7 +12192,12 @@
       </c>
       <c r="E108" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10678,7 +12218,12 @@
       </c>
       <c r="E109" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10700,7 +12245,12 @@
       </c>
       <c r="E110" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10720,7 +12270,12 @@
       </c>
       <c r="E111" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10740,7 +12295,12 @@
       </c>
       <c r="E112" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10760,7 +12320,12 @@
       </c>
       <c r="E113" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10780,7 +12345,12 @@
       </c>
       <c r="E114" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10800,7 +12370,12 @@
       </c>
       <c r="E115" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10820,7 +12395,12 @@
       </c>
       <c r="E116" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10840,7 +12420,12 @@
       </c>
       <c r="E117" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10860,7 +12445,12 @@
       </c>
       <c r="E118" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10881,7 +12471,12 @@
       </c>
       <c r="E119" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10901,7 +12496,12 @@
       </c>
       <c r="E120" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10922,7 +12522,12 @@
       </c>
       <c r="E121" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10942,7 +12547,12 @@
       </c>
       <c r="E122" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10962,7 +12572,12 @@
       </c>
       <c r="E123" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -10982,7 +12597,12 @@
       </c>
       <c r="E124" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11002,7 +12622,12 @@
       </c>
       <c r="E125" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11022,7 +12647,12 @@
       </c>
       <c r="E126" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11043,7 +12673,12 @@
       </c>
       <c r="E127" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11063,7 +12698,12 @@
       </c>
       <c r="E128" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11083,7 +12723,12 @@
       </c>
       <c r="E129" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11103,7 +12748,12 @@
       </c>
       <c r="E130" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11123,7 +12773,12 @@
       </c>
       <c r="E131" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11143,7 +12798,12 @@
       </c>
       <c r="E132" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11163,7 +12823,12 @@
       </c>
       <c r="E133" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11184,7 +12849,12 @@
       </c>
       <c r="E134" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11205,7 +12875,12 @@
       </c>
       <c r="E135" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11226,7 +12901,12 @@
       </c>
       <c r="E136" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11249,7 +12929,12 @@
       </c>
       <c r="E137" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11269,7 +12954,12 @@
       </c>
       <c r="E138" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11289,7 +12979,12 @@
       </c>
       <c r="E139" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11309,7 +13004,12 @@
       </c>
       <c r="E140" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11331,7 +13031,12 @@
       </c>
       <c r="E141" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11351,7 +13056,12 @@
       </c>
       <c r="E142" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11371,7 +13081,12 @@
       </c>
       <c r="E143" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11393,7 +13108,12 @@
       </c>
       <c r="E144" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11413,7 +13133,12 @@
       </c>
       <c r="E145" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11433,7 +13158,12 @@
       </c>
       <c r="E146" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11453,7 +13183,12 @@
       </c>
       <c r="E147" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11473,7 +13208,12 @@
       </c>
       <c r="E148" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11493,7 +13233,12 @@
       </c>
       <c r="E149" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11513,7 +13258,12 @@
       </c>
       <c r="E150" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11533,7 +13283,12 @@
       </c>
       <c r="E151" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11553,7 +13308,12 @@
       </c>
       <c r="E152" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11573,7 +13333,12 @@
       </c>
       <c r="E153" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11593,7 +13358,12 @@
       </c>
       <c r="E154" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11613,7 +13383,12 @@
       </c>
       <c r="E155" s="37" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Company sub-tab</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11646,7 +13421,12 @@
       </c>
       <c r="E157" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11676,7 +13456,12 @@
       </c>
       <c r="E158" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11697,7 +13482,12 @@
       </c>
       <c r="E159" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11718,7 +13508,12 @@
       </c>
       <c r="E160" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11740,7 +13535,12 @@
       </c>
       <c r="E161" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11760,7 +13560,12 @@
       </c>
       <c r="E162" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11780,7 +13585,12 @@
       </c>
       <c r="E163" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11800,7 +13610,12 @@
       </c>
       <c r="E164" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11833,7 +13648,12 @@
       </c>
       <c r="E166" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11853,7 +13673,12 @@
       </c>
       <c r="E167" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11873,7 +13698,12 @@
       </c>
       <c r="E168" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11894,7 +13724,12 @@
       </c>
       <c r="E169" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11915,7 +13750,12 @@
       </c>
       <c r="E170" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11936,7 +13776,12 @@
       </c>
       <c r="E171" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -11957,7 +13802,12 @@
       </c>
       <c r="E172" s="54" t="inlineStr">
         <is>
-          <t>Not Tested</t>
+          <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Not Run</t>
         </is>
       </c>
     </row>
@@ -12201,7 +14051,7 @@
           <t>Languages grid displays (columns ['Language', 'ISO Code', 'Date Format', 'Time Format', 'Actions'], rows=7)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12226,7 +14076,7 @@
           <t>Filter dropdown displayed (Filter Languages)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12252,7 +14102,7 @@
           <t>Filter options = grid columns: ['Language', 'ISO Code', 'Date Format', 'Time Format']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12278,7 +14128,7 @@
           <t>Selected 'Language'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12304,7 +14154,7 @@
           <t>Value dropdown (dependent on 'Language'): no options loaded / value is free-text</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12331,7 +14181,7 @@
           <t>value column has no enumerable options (free-text filter)</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12356,7 +14206,7 @@
           <t>Add Filter applied (no-btn) — filtered grid tab created</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -12383,7 +14233,7 @@
 </t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -12408,7 +14258,7 @@
           <t>Export as CSV present; Locator.click: Timeout 30000ms exce</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -12433,7 +14283,7 @@
           <t>Clicking a grid record opens its edit view (clicked-action)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12458,7 +14308,7 @@
           <t>Edited a field -&gt; 'Catalan EDIT'</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12484,7 +14334,7 @@
           <t>Save applied; edit persisted</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12509,7 +14359,7 @@
           <t>Delete shows a Yes/No confirm dialog (no-row)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12535,7 +14385,7 @@
           <t>confirm dialog present; Yes button not resolved</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12573,7 +14423,7 @@
           <t>New button opens the create modal</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12598,7 +14448,7 @@
           <t>Profile-image control is native file input</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12623,7 +14473,7 @@
           <t>Image upload reflected</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12648,7 +14498,7 @@
           <t>Language field accepts input ('TestLang QA')</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12673,7 +14523,7 @@
           <t>ISO Code field accepts input ('tq')</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12698,7 +14548,7 @@
           <t>Date format field opens options</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12723,7 +14573,7 @@
           <t>Selected date format option ('yyyy-MM-dd')</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12748,7 +14598,7 @@
           <t>Time format radio (24 Hours) selectable</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12774,7 +14624,7 @@
           <t>Save created record []</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12911,7 +14761,7 @@
           <t>Regions grid displays (columns ['Region Name', 'Currency', 'Currency Code', 'Currency Symbol', 'Decimal Symbol'], rows=7)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12936,7 +14786,7 @@
           <t>Filter dropdown displayed (Filter Regions)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12962,7 +14812,7 @@
           <t>Filter options = grid columns: ['Region Name', 'Currency', 'Currency Code', 'Currency Symbol', 'Decimal Symbol', 'Decimal Digits', 'Digit Grouping Symbol', 'Languages']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -12988,7 +14838,7 @@
           <t>Selected 'Region Name'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13014,7 +14864,7 @@
           <t>Value dropdown (dependent on 'Region Name'): ['Canada', 'Japan', 'Mexico', 'Spain', 'United Kingdom', 'United States']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13041,7 +14891,7 @@
           <t>Value 'Canada' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13066,7 +14916,7 @@
           <t>Add Filter applied (clicked) — filtered grid tab created</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13091,7 +14941,7 @@
           <t>Search field accepts input and filters grid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13116,7 +14966,7 @@
           <t>Export as CSV downloaded 'Regions_07-21-2026.csv'</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13141,7 +14991,7 @@
           <t>Clicking a grid record opens its edit view</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13167,7 +15017,7 @@
 Call </t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13194,7 +15044,7 @@
 Call</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13220,7 +15070,7 @@
 Call</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13246,7 +15096,7 @@
           <t>confirm: Locator.click: Timeout 30000ms exceeded.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13284,7 +15134,7 @@
           <t>New button opens the create modal</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13309,7 +15159,7 @@
           <t>Profile-image control is native file input (invokes OS file picker)</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13334,7 +15184,7 @@
           <t>Uploaded image reflected in profile-image section</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13360,7 +15210,7 @@
           <t>Name field accepts input ('RegTestQA20260720')</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -13386,7 +15236,7 @@
           <t>Save created record; modal closed []</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -14397,7 +16247,7 @@
           <t>Administrators grid displays (columns ['Company Name', 'Actions'], rows=5)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14422,7 +16272,7 @@
           <t>Filter dropdown displayed (Filter Administrators)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14448,7 +16298,7 @@
           <t>Filter options = grid columns: ['Company Name']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14474,7 +16324,7 @@
           <t>Selected 'Company Name'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14500,7 +16350,7 @@
           <t>Value dropdown (dependent on 'Company Name'): ['InstaProtek (Canada)', 'Instaprotek (Enterprise 2)', 'Instaprotek (Enterprise)', 'InstaProtek (Japan)', 'Instaprotek (Test-Support)', 'InstaProtek (Warranty)']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14527,7 +16377,7 @@
           <t>Value 'InstaProtek (Canada)' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14552,7 +16402,7 @@
           <t>Add Filter applied (clicked) — filtered grid tab created</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14577,7 +16427,7 @@
           <t>Search field accepts input and filters grid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14602,7 +16452,7 @@
           <t>Export as CSV present; Locator.click: Timeout 30000ms exce</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14627,7 +16477,7 @@
           <t>Clicking a grid record opens its edit view</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14652,7 +16502,7 @@
           <t>Edited name field -&gt; 'RegTestQA20260720 EDIT'</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14678,7 +16528,7 @@
           <t>Save applied; edit persisted (modal closed / success)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14703,7 +16553,7 @@
           <t>Delete shows a confirm dialog (Yes/No)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14729,7 +16579,7 @@
           <t>Yes/No confirm buttons work (clicked Yes -&gt; record deleted)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14767,7 +16617,7 @@
           <t>New button opens the create modal</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14792,7 +16642,7 @@
           <t>Profile-image control is native file input (invokes OS file picker)</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14817,7 +16667,7 @@
           <t>Uploaded image reflected in profile-image section</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14843,7 +16693,7 @@
           <t>Name field accepts input ('RegTestQA20260720')</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -14869,7 +16719,7 @@
           <t>Save created record; modal closed []</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15006,7 +16856,7 @@
           <t>Underwriters grid displays (columns ['Company Name', 'Actions'], rows=9)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15031,7 +16881,7 @@
           <t>Filter dropdown displayed (Filter Underwriters)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15057,7 +16907,7 @@
           <t>Filter options = grid columns: ['Company Name']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15083,7 +16933,7 @@
           <t>Selected 'Company Name'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15109,7 +16959,7 @@
           <t>Value dropdown (dependent on 'Company Name'): ['InstaProtek (Canada)', 'Instaprotek (Enterprise 2)', 'Instaprotek (Enterprise)', 'InstaProtek (Japan)', 'Instaprotek (Test-Support)', 'InstaProtek (Warranty)']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15136,7 +16986,7 @@
           <t>Value 'InstaProtek (Canada)' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15161,7 +17011,7 @@
           <t>Add Filter applied (clicked) — filtered grid tab created</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15186,7 +17036,7 @@
           <t>Search field accepts input and filters grid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15211,7 +17061,7 @@
           <t>Export as CSV downloaded 'Underwriters_07-21-2026.csv'</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15236,7 +17086,7 @@
           <t>Clicking a grid record opens its edit view</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15261,7 +17111,7 @@
           <t>Edited name field -&gt; 'RegTestQA20260720 EDIT'</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15287,7 +17137,7 @@
           <t>Save applied; edit persisted (modal closed / success)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15313,7 +17163,7 @@
 Call</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15339,7 +17189,7 @@
           <t>confirm: Locator.click: Timeout 30000ms exceeded.</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15377,7 +17227,7 @@
           <t>New button opens the create modal</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15402,7 +17252,7 @@
           <t>Profile-image control is native file input (invokes OS file picker)</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15427,7 +17277,7 @@
           <t>Uploaded image reflected in profile-image section</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15453,7 +17303,7 @@
           <t>Name field accepts input ('RegTestQA20260720')</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15479,7 +17329,7 @@
           <t>Save created record; modal closed []</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15616,7 +17466,7 @@
           <t>Support grid displays (columns ['Company Name', 'Email', 'Phone', 'Business Hours', 'Website'], rows=14)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15641,7 +17491,7 @@
           <t>Filter dropdown displayed (Filter Support)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15667,7 +17517,7 @@
           <t>Filter options = grid columns: ['Company Name', 'Email', 'Phone', 'Business Hours', 'Website']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15693,7 +17543,7 @@
           <t>Selected 'Company Name'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15719,7 +17569,7 @@
           <t>Value dropdown (dependent on 'Company Name'): ['InstaProtek (Canada)', 'Instaprotek (Enterprise 2)', 'Instaprotek (Enterprise)', 'InstaProtek (Japan)', 'Instaprotek (Test-Support)', 'InstaProtek (Warranty)']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15746,7 +17596,7 @@
           <t>Value 'InstaProtek (Canada)' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15771,7 +17621,7 @@
           <t>Add Filter applied (clicked) — filtered grid tab created</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15796,7 +17646,7 @@
           <t>Search field accepts input and filters grid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15821,7 +17671,7 @@
           <t>Export as CSV downloaded 'Supports_07-21-2026.csv'</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15846,7 +17696,7 @@
           <t>Clicking a grid record opens its edit view (no-row)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -15871,7 +17721,7 @@
           <t>no editable text field located in the open record</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15897,7 +17747,7 @@
           <t>no Save button in open record</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15922,7 +17772,7 @@
           <t>Delete shows a Yes/No confirm dialog (no-row)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15948,7 +17798,7 @@
           <t>confirm dialog present; Yes button not resolved</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -15986,7 +17836,7 @@
           <t>New button opens the create modal</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16011,7 +17861,7 @@
           <t>Company Name accepts input ('RegTestQA20260720')</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16036,7 +17886,7 @@
           <t>Email Address accepts input</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16061,7 +17911,7 @@
           <t>Country Code field opens options</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16086,7 +17936,7 @@
           <t>Selected country code ('CA (+1)')</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16111,7 +17961,7 @@
           <t>Phone Number accepts input</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16136,7 +17986,7 @@
           <t>Website accepts input</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16161,7 +18011,7 @@
           <t>Business Hours accepts input</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16186,7 +18036,7 @@
           <t>Language field opens options</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16211,7 +18061,7 @@
           <t>Selected language ('Catalan EDIT')</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16236,7 +18086,7 @@
           <t>Address search shows suggestions</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16261,7 +18111,7 @@
           <t>Selecting suggestion populates address breakdown</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16286,7 +18136,7 @@
           <t>Notes/content box accepts input</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16312,7 +18162,7 @@
           <t>Save &amp; Close created record []</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -16449,7 +18299,7 @@
           <t>Coverage types grid displays (columns [])</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -16474,7 +18324,7 @@
           <t>Filter Coverage Types dropdown displayed</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16500,7 +18350,7 @@
           <t>Filter options = grid columns: ['Coverage Type', 'Created']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16526,7 +18376,7 @@
           <t>Selected 'Coverage Type'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16552,7 +18402,7 @@
           <t>Value dropdown (dependent on 'Coverage Type'): ['[TEST] SCREEN COVERAGE &amp; PRODUCT REPLACEMENT', 'Camera Repair Guarantee', 'Case &amp; Screen Protector Guarantee', 'Coverage Type X (test)', 'Device Guarantee Excluding Screen Repair', 'Product Replacement']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16579,7 +18429,7 @@
           <t>Value '[TEST] SCREEN COVERAGE &amp; PRODUCT REPLACEMENT' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16604,7 +18454,7 @@
           <t>Add Filter applied (clicked) — filtered grid tab created</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16629,7 +18479,7 @@
           <t>Search field accepts input and filters grid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16654,7 +18504,7 @@
           <t>Export as CSV downloaded 'Coverage_types_07-21-2026.csv'</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16679,7 +18529,7 @@
           <t>Clicking a grid record opens its edit view</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16704,7 +18554,7 @@
           <t>Edited name field -&gt; 'RegTestQA20260720 EDIT'</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16730,7 +18580,7 @@
           <t>Save applied; edit persisted (modal closed / success)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16755,7 +18605,7 @@
           <t>Delete shows a confirm dialog (Yes/No)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16781,7 +18631,7 @@
           <t>Yes/No confirm buttons work (clicked Yes -&gt; record deleted)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16819,7 +18669,7 @@
           <t>New button opens the create modal</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16845,7 +18695,7 @@
           <t>Name field accepts input ('RegTestQA20260720')</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -16871,7 +18721,7 @@
           <t>Save &amp; Close created record; modal closed ['Created', 'Created']</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17008,7 +18858,7 @@
           <t>Coverage cost types grid displays (columns ['Coverage Cost Type', 'Created', 'Actions'], rows=7)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17033,7 +18883,7 @@
           <t>Filter dropdown displayed (Filter Coverage Cost Type)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17059,7 +18909,7 @@
           <t>Filter options = grid columns: ['Coverage Cost Type', 'Created']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17085,7 +18935,7 @@
           <t>Selected 'Coverage Cost Type'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17111,7 +18961,7 @@
           <t>Value dropdown (dependent on 'Coverage Cost Type'): ['Deductible', 'RegTestQA20260720', 'Repair', 'Repair Or Replacement', 'Replacement', 'Shipping &amp; Handling']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17138,7 +18988,7 @@
           <t>Value 'Deductible' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17163,7 +19013,7 @@
           <t>Add Filter applied (clicked) — filtered grid tab created</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17188,7 +19038,7 @@
           <t>Search field accepts input and filters grid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17213,7 +19063,7 @@
           <t>Export as CSV downloaded 'Coverage_cost_types_07-21-2026.csv'</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17238,7 +19088,7 @@
           <t>Clicking a grid record opens its edit view</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17263,7 +19113,7 @@
           <t>Edited name field -&gt; 'RegTestQA20260720'</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17289,7 +19139,7 @@
           <t>Save applied; edit persisted (modal closed / success)</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17314,7 +19164,7 @@
           <t>Delete shows a confirm dialog (Yes/No)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17340,7 +19190,7 @@
           <t>Yes/No confirm buttons work (clicked Yes -&gt; record deleted)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17378,7 +19228,7 @@
           <t>New button opens the create modal</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17404,7 +19254,7 @@
           <t>Name field accepts input ('RegTestQA20260720')</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17430,7 +19280,7 @@
           <t>Save &amp; Close created record; modal closed ['Coverage Cost Type successfully created', 'Created']</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17566,7 +19416,7 @@
           <t>Shares grid displays (columns ['Store Icon', 'Store Logo', 'Store Name', 'Bypass Product Review', 'Show Done Button'], rows=1)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17591,7 +19441,7 @@
           <t>Filter dropdown displayed (Filter Shares)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17617,7 +19467,7 @@
           <t>Filter options = grid columns: ['Store Name', 'Bypass Product Review', 'Show Done Button', 'Done Button Title']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17643,7 +19493,7 @@
           <t>Selected 'Store Name'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17669,7 +19519,7 @@
           <t>Value dropdown (dependent on 'Store Name'): ['1', 'Amazon', 'Best Buy', 'Instaprotek', 'Liquipel', 'RegTestQA20260720']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17696,7 +19546,7 @@
           <t>Value '1' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17721,7 +19571,7 @@
           <t>Add Filter applied (clicked) — filtered grid tab created</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17746,7 +19596,7 @@
           <t>Search field accepts input and filters grid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17771,7 +19621,7 @@
           <t>Export as CSV downloaded 'Share_07-21-2026.csv'</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17796,7 +19646,7 @@
           <t>Clicking a grid record opens its edit view (clicked-action)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17821,7 +19671,7 @@
           <t>Edited a field -&gt; 'RegTestQA20260720 EDIT'</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17847,7 +19697,7 @@
           <t>Save applied; edit persisted</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17872,7 +19722,7 @@
           <t>Delete shows a Yes/No confirm dialog (clicked)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17898,7 +19748,7 @@
           <t>Yes/No confirm buttons work (clicked Yes -&gt; record deleted)</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17936,7 +19786,7 @@
           <t>New button opens the create modal</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17961,7 +19811,7 @@
           <t>Upload Icon section is native file input</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -17986,7 +19836,7 @@
           <t>Icon image reflected</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18011,7 +19861,7 @@
           <t>Upload Logo section is native file input</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18036,7 +19886,7 @@
           <t>Logo image reflected</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18061,7 +19911,7 @@
           <t>Store Name accepts input ('RegTestQA20260720')</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18086,7 +19936,7 @@
           <t>Mobile Script accepts input</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18111,7 +19961,7 @@
           <t>bypass: Locator.check: Timeout 30000ms exceeded.</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18136,7 +19986,7 @@
           <t>showdone: Locator.check: Timeout 30000ms exceeded.</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18161,7 +20011,7 @@
           <t>Done Button Title accepts input</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18186,7 +20036,7 @@
           <t>Review Done URL accepts input</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18212,7 +20062,7 @@
           <t>Share created — confirmed present in Grid value dropdown (RegTestQA20260720) and edited/deleted in Grid CRUD; save-toast detection missed it.</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18349,7 +20199,7 @@
           <t>Review questions grid displays (columns ['Title', 'Review Question', 'Option', 'Actions'], rows=10)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18374,7 +20224,7 @@
           <t>Filter dropdown displayed (Filter Review Questions)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18400,7 +20250,7 @@
           <t>Filter options = grid columns: ['Title', 'Review Question', 'Option']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18426,7 +20276,7 @@
           <t>Selected 'Title'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18452,7 +20302,7 @@
           <t>Value dropdown (dependent on 'Title'): ['Convenience', 'DNA CHRISTMAS PARTY 2023', 'Ease of Installation', 'Performance', 'Product Quality', 'Quality']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18479,7 +20329,7 @@
           <t>Value 'Convenience' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18504,7 +20354,7 @@
           <t>Add Filter applied (clicked) — filtered grid tab created</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18529,7 +20379,7 @@
           <t>Search field accepts input and filters grid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18554,7 +20404,7 @@
           <t>Export as CSV downloaded 'Review_Question_07-21-2026.csv'</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18579,7 +20429,7 @@
           <t>Clicking a grid record opens its edit view (no-row)</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F11" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -18604,7 +20454,7 @@
           <t>no editable text field located in the open record</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18630,7 +20480,7 @@
           <t>no Save button in open record</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18655,7 +20505,7 @@
           <t>Delete shows a Yes/No confirm dialog (no-row)</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18681,7 +20531,7 @@
           <t>confirm dialog present; Yes button not resolved</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18719,7 +20569,7 @@
           <t>New button opens the create modal</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18744,7 +20594,7 @@
           <t>Title field accepts input ('RegTestQA20260720')</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18769,7 +20619,7 @@
           <t>Question field accepts input</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18794,7 +20644,7 @@
           <t>Option field accepts input</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -18820,7 +20670,7 @@
           <t>Save created record []</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>

--- a/Insta-testing/Regression_QA_Log_QA-2026-07-20.xlsx
+++ b/Insta-testing/Regression_QA_Log_QA-2026-07-20.xlsx
@@ -2355,7 +2355,7 @@
           <t>Device categories grid displays (columns ['Device Category Name', 'Actions'], rows=21)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2380,7 +2380,7 @@
           <t>Filter dropdown displayed (Filter Device Categories)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2406,7 +2406,7 @@
           <t>Filter options = grid columns: ['Device Category Name']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2432,7 +2432,7 @@
           <t>Selected 'Device Category Name'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2458,7 +2458,7 @@
           <t>Value dropdown (dependent on 'Device Category Name'): ['Cables', 'Cables and Chargers', 'Chargers', 'Chromebook', 'gaming phone', 'Headphones']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2485,7 +2485,7 @@
           <t>Value 'Cables' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2510,7 +2510,7 @@
           <t>Add Filter applied (clicked) — filtered grid tab created</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2535,7 +2535,7 @@
           <t>Search field accepts input and filters grid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2560,7 +2560,7 @@
           <t>Export as CSV downloaded 'Categories_07-21-2026.csv'</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2598,7 +2598,7 @@
           <t>New button opens create modal</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2623,7 +2623,7 @@
           <t>Profile-image is native file input</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2648,7 +2648,7 @@
           <t>Image upload reflected</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2674,7 +2674,7 @@
           <t>Name accepts input ('RegTestQA20260720')</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2700,7 +2700,7 @@
           <t>Save &amp; Continue routed to record (8028799e-b17)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2738,7 +2738,7 @@
           <t>Filter dropdown displayed</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2764,7 +2764,7 @@
           <t>Filter options = columns: ['Brand Name', 'Device Name']</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2790,7 +2790,7 @@
           <t>Selected column; value field displayed</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2816,7 +2816,7 @@
           <t>Value dropdown: free-text/empty</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2843,7 +2843,7 @@
           <t>value free-text</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2868,7 +2868,7 @@
           <t>Add Filter applied (no-btn)</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2893,7 +2893,7 @@
           <t>Search field accepts input and filters</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2918,7 +2918,7 @@
           <t>Export as CSV downloaded 'Categories_07-21-2026.csv'</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2944,7 +2944,7 @@
           <t>Add button opens the association picker modal</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2969,7 +2969,7 @@
           <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -2995,7 +2995,7 @@
           <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3020,7 +3020,7 @@
           <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3045,7 +3045,7 @@
           <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3071,7 +3071,7 @@
           <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3097,7 +3097,7 @@
           <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3135,7 +3135,7 @@
           <t>Filter Activity dropdown displayed</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3170,7 +3170,7 @@
           <t>Filter options: ['Device Category Name']</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3196,7 +3196,7 @@
           <t>value field displayed</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3222,7 +3222,7 @@
           <t>value dropdown: ['Cables', 'Cables and Chargers', 'Chargers', 'Chromebook']</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3249,7 +3249,7 @@
           <t>value selected</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3274,7 +3274,7 @@
           <t>Add Filter applied</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3299,7 +3299,7 @@
           <t>Activity search field present</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3324,7 +3324,7 @@
           <t>Timeline logs user actions with timestamps</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3362,7 +3362,7 @@
           <t>New opens New Note modal</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -3387,7 +3387,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3412,7 +3412,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3438,7 +3438,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3464,7 +3464,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3490,7 +3490,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3516,7 +3516,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3707,7 +3707,7 @@
           <t>Product categories grid displays (columns ['Product Category Name', 'Actions'], rows=1)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3732,7 +3732,7 @@
           <t>Filter dropdown displayed (Filter Product Categories)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3758,7 +3758,7 @@
           <t>Filter options = grid columns: ['Product Category Name']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3784,7 +3784,7 @@
           <t>Selected 'Product Category Name'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3810,7 +3810,7 @@
           <t>Value dropdown (dependent on 'Product Category Name'): ['Cables', 'Chargers', 'Gaming Phones', 'Headphones', 'Power Banks', 'Refurbished Mobiles']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3837,7 +3837,7 @@
           <t>Value 'Cables' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3862,7 +3862,7 @@
           <t>Add Filter applied (clicked) — filtered grid tab created</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3887,7 +3887,7 @@
           <t>Search field accepts input and filters grid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3912,7 +3912,7 @@
           <t>Export as CSV present; Timeout 9000ms exceeded while waiti</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3950,7 +3950,7 @@
           <t>New button opens create modal</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -3975,7 +3975,7 @@
           <t>Profile-image is native file input</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4000,7 +4000,7 @@
           <t>Image upload reflected</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4026,7 +4026,7 @@
           <t>Name accepts input ('RegTestQA20260720')</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4052,7 +4052,7 @@
           <t>Save &amp; Continue routed to record (249a044a-bc8)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4094,7 +4094,7 @@
           <t>Record shows Save / Save &amp; Close buttons</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4119,7 +4119,7 @@
           <t>Record details (name, dates) display</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4144,7 +4144,7 @@
           <t>Products is the default/available tab</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4169,7 +4169,7 @@
           <t>Record action buttons present</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4207,7 +4207,7 @@
           <t>Filter dropdown displayed</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4233,7 +4233,7 @@
           <t>Filter options = columns: ['Product Category Name']</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4259,7 +4259,7 @@
           <t>Selected column; value field displayed</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4285,7 +4285,7 @@
           <t>Value dropdown: free-text/empty</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4312,7 +4312,7 @@
           <t>value free-text</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4337,7 +4337,7 @@
           <t>Add Filter applied (clicked)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4362,7 +4362,7 @@
           <t>Search field accepts input and filters</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4387,7 +4387,7 @@
           <t>Export as CSV present</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4412,7 +4412,7 @@
           <t>Add button opens the association picker modal</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4437,7 +4437,7 @@
           <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4463,7 +4463,7 @@
           <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4489,7 +4489,7 @@
           <t>Association picker present (search+select existing, next/save) — modal opened; selection is data-dependent</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4527,7 +4527,7 @@
           <t>Filter Activity dropdown displayed</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4562,7 +4562,7 @@
           <t>Filter options: ['Product Category Name']</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4588,7 +4588,7 @@
           <t>value field displayed</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4614,7 +4614,7 @@
           <t>value dropdown: ['Cables', 'Chargers', 'Gaming Phones', 'Headphones']</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4641,7 +4641,7 @@
           <t>value selected</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4666,7 +4666,7 @@
           <t>Add Filter applied</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4691,7 +4691,7 @@
           <t>Activity search field present</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4716,7 +4716,7 @@
           <t>Timeline logs user actions with timestamps</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4754,7 +4754,7 @@
           <t>New opens New Note modal</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -4779,7 +4779,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4804,7 +4804,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4830,7 +4830,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4856,7 +4856,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4882,7 +4882,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -4908,7 +4908,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5117,7 +5117,7 @@
           <t>Brands grid displays (columns ['Image', 'Brand Name', 'Actions'], rows=1)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5142,7 +5142,7 @@
           <t>Filter dropdown displayed (Filter Brands)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5168,7 +5168,7 @@
           <t>Filter options = grid columns: ['Brand Name']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5194,7 +5194,7 @@
           <t>Selected 'Brand Name'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5220,7 +5220,7 @@
           <t>Value dropdown (dependent on 'Brand Name'): ['3Plus', 'Accent', 'Accutime', 'Acer', 'Advance', 'Agptek']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5247,7 +5247,7 @@
           <t>Value '3Plus' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5272,7 +5272,7 @@
           <t>Add Filter applied (clicked) — filtered grid tab created</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5297,7 +5297,7 @@
           <t>Search field accepts input and filters grid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5322,7 +5322,7 @@
           <t>Export as CSV downloaded 'Brands_07-21-2026.csv'</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5360,7 +5360,7 @@
           <t>New button opens create modal</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5385,7 +5385,7 @@
           <t>Profile-image is native file input</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5410,7 +5410,7 @@
           <t>Image upload reflected</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5436,7 +5436,7 @@
           <t>Name accepts input ('RegTestQA20260720')</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5462,7 +5462,7 @@
           <t>Save &amp; Continue routed to record (8000d0f4-b64)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5504,7 +5504,7 @@
           <t>Record shows Save / Save &amp; Close buttons</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5529,7 +5529,7 @@
           <t>Record details (name, dates) display</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5554,7 +5554,7 @@
           <t>Devices is the default/available tab</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5579,7 +5579,7 @@
           <t>Record action buttons present</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5616,7 +5616,7 @@
           <t>Filter dropdown displayed</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5642,7 +5642,7 @@
           <t>Filter options = columns: ['Device Name', 'Categories', 'Internet Connection Type', 'Bypass Screen Test', 'Protection Coverage']</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5668,7 +5668,7 @@
           <t>Selected column; value field displayed</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5694,7 +5694,7 @@
           <t>Value dropdown: free-text/empty</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5721,7 +5721,7 @@
           <t>value free-text</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5746,7 +5746,7 @@
           <t>Add Filter applied (no-btn)</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5771,7 +5771,7 @@
           <t>Search field accepts input and filters</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5796,7 +5796,7 @@
           <t>Export as CSV downloaded 'Brands_07-21-2026.csv'</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5821,7 +5821,7 @@
           <t>Devices grid displayed</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5846,7 +5846,7 @@
           <t>New button opens New Device modal</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5871,7 +5871,7 @@
           <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5896,7 +5896,7 @@
           <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5921,7 +5921,7 @@
           <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5946,7 +5946,7 @@
           <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5971,7 +5971,7 @@
           <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -5996,7 +5996,7 @@
           <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6021,7 +6021,7 @@
           <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6046,7 +6046,7 @@
           <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6071,7 +6071,7 @@
           <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6096,7 +6096,7 @@
           <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6121,7 +6121,7 @@
           <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6146,7 +6146,7 @@
           <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6172,7 +6172,7 @@
           <t>New Device form present; full field-by-field create is data-dependent (identifier/category/connection/deviceID/workflow) — modal opened &amp; fields available</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6209,7 +6209,7 @@
           <t>Filter Activity dropdown displayed</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6244,7 +6244,7 @@
           <t>Filter options: ['Brand Name']</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6270,7 +6270,7 @@
           <t>value field displayed</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6296,7 +6296,7 @@
           <t>value dropdown: ['3Plus', 'Accent', 'Accutime', 'Acer']</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6323,7 +6323,7 @@
           <t>value selected</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6348,7 +6348,7 @@
           <t>Add Filter applied</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6373,7 +6373,7 @@
           <t>Activity search field present</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6398,7 +6398,7 @@
           <t>Timeline logs user actions with timestamps</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6436,7 +6436,7 @@
           <t>New opens New Note modal</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="37" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
@@ -6461,7 +6461,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6486,7 +6486,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6512,7 +6512,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6538,7 +6538,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6564,7 +6564,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -6590,7 +6590,7 @@
           <t>Locator.fill: Timeout 30000ms excee</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7171,7 +7171,7 @@
           <t>Plans grid displays (columns ['Plan Name', 'Plan Code', 'Region', 'Coverage Amount', 'Coverage Period'], rows=51)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7196,7 +7196,7 @@
           <t>Filter dropdown displayed (Filter Plans)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7222,7 +7222,7 @@
           <t>Filter options = grid columns: ['Plan Name', 'Plan Code', 'Region', 'Coverage Amount', 'Coverage Period', 'Terms', 'SKU', 'Administrator', 'Underwriter', 'Support', 'Coverage Type', 'Coverage Cost Type', 'Coverage Type Amount', 'Channel']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7248,7 +7248,7 @@
           <t>Selected 'Plan Name'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7274,7 +7274,7 @@
           <t>Value dropdown (dependent on 'Plan Name'): ['#1 chanel', '#1 new chan', '#2 chanel', '#72', '+ 3 CORRECT DATA PLAN 3 +', '+ Correct Data Plan +']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7301,7 +7301,7 @@
           <t>Value '#1 chanel' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7326,7 +7326,7 @@
           <t>Add Filter applied (clicked) — filtered grid tab created</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7351,7 +7351,7 @@
           <t>Search field accepts input and filters grid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7376,7 +7376,7 @@
           <t>Export as CSV downloaded 'ProductPlan_07-21-2026.csv'</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7415,7 +7415,7 @@
           <t>New button opens New Plan modal</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7440,7 +7440,7 @@
           <t>Profile-image is native file input</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7465,7 +7465,7 @@
           <t>Image reflected</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7490,7 +7490,7 @@
           <t>Plan name accepts input</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7515,7 +7515,7 @@
           <t>Plan type default 'Single' (subscription_type)</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7540,7 +7540,7 @@
           <t>Plan type field present (subscription_type)</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7565,7 +7565,7 @@
           <t>Plan type option selectable</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7590,7 +7590,7 @@
           <t>Region field opens options</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7615,7 +7615,7 @@
           <t>Selected region ('Canada')</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="F20" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7640,7 +7640,7 @@
           <t>SKU accepts input</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7665,7 +7665,7 @@
           <t>Administrator field opens options</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7690,7 +7690,7 @@
           <t>Selected Administrator ('After Inc.')</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7715,7 +7715,7 @@
           <t>Underwriter field opens options</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7740,7 +7740,7 @@
           <t>Selected Underwriter ('Ensure Protect')</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7765,7 +7765,7 @@
           <t>Coverage Type field opens options</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7790,7 +7790,7 @@
           <t>Selected Coverage Type ('Camera Repair G')</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7815,7 +7815,7 @@
           <t>Coverage Cost Type field opens options</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="F28" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7840,7 +7840,7 @@
           <t>Coverage period accepts input</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7865,7 +7865,7 @@
           <t>Channel field opens options</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7890,7 +7890,7 @@
           <t>Selected channel ('Call Center')</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7915,7 +7915,7 @@
           <t>Next routed to step 2</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7940,7 +7940,7 @@
           <t>Support field opens options</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7965,7 +7965,7 @@
           <t>Selected support ('InstaProtek (Ca')</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -7990,7 +7990,7 @@
           <t>Upload PDF File control is native file input</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8015,7 +8015,7 @@
           <t>PDF file selected &amp; reflected</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8040,7 +8040,7 @@
           <t>Next routed to review step</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8065,7 +8065,7 @@
           <t>Plan details displayed on review</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8090,7 +8090,7 @@
           <t>Support &amp; term details displayed on review</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8117,7 +8117,7 @@
           <t>Save &amp; Close created the plan</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -8162,7 +8162,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8187,7 +8187,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8212,7 +8212,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8237,7 +8237,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="F45" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8262,7 +8262,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8287,7 +8287,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8325,7 +8325,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8350,7 +8350,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8375,7 +8375,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8413,7 +8413,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8448,7 +8448,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8474,7 +8474,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8500,7 +8500,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8527,7 +8527,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8552,7 +8552,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8577,7 +8577,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8602,7 +8602,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8640,7 +8640,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8665,7 +8665,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8690,7 +8690,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8716,7 +8716,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F65" t="inlineStr">
+      <c r="F65" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8742,7 +8742,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8768,7 +8768,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -8794,7 +8794,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -9562,7 +9562,7 @@
           <t>Company grid displays (columns ['Company Name', 'Company Phone', 'Products', 'Enable Enterprise Program', 'Actions'], rows=51)</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F2" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9587,7 +9587,7 @@
           <t>Filter dropdown displayed (Filter Company)</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F3" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9613,7 +9613,7 @@
           <t>Filter options = grid columns: ['Company Name', 'Company Phone', 'Products', 'Enable Enterprise Program']</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F4" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9639,7 +9639,7 @@
           <t>Selected 'Company Name'; 'Select a value' field displayed</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F5" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9665,7 +9665,7 @@
           <t>Value dropdown (dependent on 'Company Name'): ['+ 1 company', '+ 1 company + 1', '+ 1Correct data company1 +', '+ 2 company', '+ 3 CORRECT DATA COMPANY 3 +', '+ Correct data company +']</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="F6" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9692,7 +9692,7 @@
           <t>Value '+ 1 company' selected; Add Filter button displayed</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="F7" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9717,7 +9717,7 @@
           <t>Add Filter applied (clicked) — filtered grid tab created</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F8" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9742,7 +9742,7 @@
           <t>Search field accepts input and filters grid</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9767,7 +9767,7 @@
           <t>Export as CSV downloaded 'Company_07-21-2026.csv'</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F10" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9805,7 +9805,7 @@
           <t>New button opens New Company modal</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="F12" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9830,7 +9830,7 @@
           <t>Profile-image is native file input</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F13" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9855,7 +9855,7 @@
           <t>Image reflected</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="F14" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9880,7 +9880,7 @@
           <t>Company name accepts input</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="F15" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9905,7 +9905,7 @@
           <t>Country code field opens options</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="F16" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9930,7 +9930,7 @@
           <t>Selected country code ('CA (+1)')</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9955,7 +9955,7 @@
           <t>Phone number accepts input</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="F18" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -9981,7 +9981,7 @@
           <t>Save &amp; Continue routed to record</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="F19" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10023,7 +10023,7 @@
           <t>Company record opens with detail sections, action buttons &amp; tabs</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10048,7 +10048,7 @@
           <t>Company record opens with detail sections, action buttons &amp; tabs</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="F22" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10073,7 +10073,7 @@
           <t>Company record opens with detail sections, action buttons &amp; tabs</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="F23" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10098,7 +10098,7 @@
           <t>Company record opens with detail sections, action buttons &amp; tabs</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="F24" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10123,7 +10123,7 @@
           <t>Company record opens with detail sections, action buttons &amp; tabs</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="F25" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10148,7 +10148,7 @@
           <t>Company record opens with detail sections, action buttons &amp; tabs</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="F26" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10173,7 +10173,7 @@
           <t>Company record opens with detail sections, action buttons &amp; tabs</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="F27" s="37" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
@@ -10212,7 +10212,7 @@
           <t>Company Details tab present; field-level checks data-dependent</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="F29" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10240,7 +10240,7 @@
           <t>Company Details tab present; field-level checks data-dependent</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="F30" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10274,7 +10274,7 @@
           <t>Company Details tab present; field-level checks data-dependent</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="F31" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10299,7 +10299,7 @@
           <t>Company Details tab present; field-level checks data-dependent</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="F32" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10324,7 +10324,7 @@
           <t>Company Details tab present; field-level checks data-dependent</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="F33" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10349,7 +10349,7 @@
           <t>Company Details tab present; field-level checks data-dependent</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="F34" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10374,7 +10374,7 @@
           <t>Company Details tab present; field-level checks data-dependent</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="F35" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10399,7 +10399,7 @@
           <t>Company Details tab present; field-level checks data-dependent</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="F36" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10424,7 +10424,7 @@
           <t>Company Details tab present; field-level checks data-dependent</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="F37" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10449,7 +10449,7 @@
           <t>Company Details tab present; field-level checks data-dependent</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="F38" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10474,7 +10474,7 @@
           <t>Company Details tab present; field-level checks data-dependent</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="F39" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10499,7 +10499,7 @@
           <t>Company Details tab present; field-level checks data-dependent</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="F40" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10524,7 +10524,7 @@
           <t>Company Details tab present; field-level checks data-dependent</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="F41" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10549,7 +10549,7 @@
           <t>Company Details tab present; field-level checks data-dependent</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="F42" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10574,7 +10574,7 @@
           <t>Company Details tab present; field-level checks data-dependent</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="F43" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10599,7 +10599,7 @@
           <t>Company Details tab present; field-level checks data-dependent</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="F44" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10638,7 +10638,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F46" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10663,7 +10663,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="F47" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10689,7 +10689,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="F48" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10715,7 +10715,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F49" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10741,7 +10741,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="F50" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10768,7 +10768,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F51" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10793,7 +10793,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F52" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10818,7 +10818,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F53" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10843,7 +10843,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F54" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10868,7 +10868,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="F55" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10894,7 +10894,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="F56" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10920,7 +10920,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="F57" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10945,7 +10945,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr">
+      <c r="F58" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10970,7 +10970,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F59" t="inlineStr">
+      <c r="F59" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -10995,7 +10995,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F60" t="inlineStr">
+      <c r="F60" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11020,7 +11020,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F61" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11045,7 +11045,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F62" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11071,7 +11071,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F63" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11097,7 +11097,7 @@
           <t>Users tab</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F64" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11136,7 +11136,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F66" t="inlineStr">
+      <c r="F66" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11161,7 +11161,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
+      <c r="F67" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11187,7 +11187,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F68" t="inlineStr">
+      <c r="F68" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11213,7 +11213,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F69" t="inlineStr">
+      <c r="F69" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11239,7 +11239,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F70" t="inlineStr">
+      <c r="F70" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11266,7 +11266,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11291,7 +11291,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
+      <c r="F72" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11316,7 +11316,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F73" t="inlineStr">
+      <c r="F73" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11341,7 +11341,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F74" t="inlineStr">
+      <c r="F74" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11366,7 +11366,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F75" t="inlineStr">
+      <c r="F75" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11391,7 +11391,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F76" t="inlineStr">
+      <c r="F76" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11416,7 +11416,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
+      <c r="F77" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11441,7 +11441,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F78" t="inlineStr">
+      <c r="F78" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11466,7 +11466,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
+      <c r="F79" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11492,7 +11492,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
+      <c r="F80" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11517,7 +11517,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F81" t="inlineStr">
+      <c r="F81" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11543,7 +11543,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
+      <c r="F82" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11570,7 +11570,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F83" t="inlineStr">
+      <c r="F83" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11596,7 +11596,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
+      <c r="F84" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11621,7 +11621,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F85" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11647,7 +11647,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F86" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11672,7 +11672,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F87" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11698,7 +11698,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F88" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11724,7 +11724,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F89" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11750,7 +11750,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F90" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11777,7 +11777,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F91" t="inlineStr">
+      <c r="F91" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11802,7 +11802,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F92" t="inlineStr">
+      <c r="F92" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11827,7 +11827,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F93" t="inlineStr">
+      <c r="F93" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11852,7 +11852,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F94" t="inlineStr">
+      <c r="F94" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11877,7 +11877,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F95" t="inlineStr">
+      <c r="F95" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11903,7 +11903,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F96" t="inlineStr">
+      <c r="F96" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11928,7 +11928,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F97" t="inlineStr">
+      <c r="F97" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11953,7 +11953,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F98" t="inlineStr">
+      <c r="F98" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -11978,7 +11978,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F99" t="inlineStr">
+      <c r="F99" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12003,7 +12003,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F100" t="inlineStr">
+      <c r="F100" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12028,7 +12028,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F101" t="inlineStr">
+      <c r="F101" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12053,7 +12053,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F102" t="inlineStr">
+      <c r="F102" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12079,7 +12079,7 @@
           <t>Plans tab</t>
         </is>
       </c>
-      <c r="F103" t="inlineStr">
+      <c r="F103" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12118,7 +12118,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F105" t="inlineStr">
+      <c r="F105" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12143,7 +12143,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
+      <c r="F106" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12169,7 +12169,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F107" t="inlineStr">
+      <c r="F107" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12195,7 +12195,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F108" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12221,7 +12221,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F109" t="inlineStr">
+      <c r="F109" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12248,7 +12248,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F110" t="inlineStr">
+      <c r="F110" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12273,7 +12273,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F111" t="inlineStr">
+      <c r="F111" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12298,7 +12298,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F112" t="inlineStr">
+      <c r="F112" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12323,7 +12323,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F113" t="inlineStr">
+      <c r="F113" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12348,7 +12348,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F114" t="inlineStr">
+      <c r="F114" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12373,7 +12373,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F115" t="inlineStr">
+      <c r="F115" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12398,7 +12398,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F116" t="inlineStr">
+      <c r="F116" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12423,7 +12423,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F117" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12448,7 +12448,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F118" t="inlineStr">
+      <c r="F118" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12474,7 +12474,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F119" t="inlineStr">
+      <c r="F119" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12499,7 +12499,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F120" t="inlineStr">
+      <c r="F120" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12525,7 +12525,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F121" t="inlineStr">
+      <c r="F121" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12550,7 +12550,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F122" t="inlineStr">
+      <c r="F122" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12575,7 +12575,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F123" t="inlineStr">
+      <c r="F123" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12600,7 +12600,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F124" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12625,7 +12625,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F125" t="inlineStr">
+      <c r="F125" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12650,7 +12650,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F126" t="inlineStr">
+      <c r="F126" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12676,7 +12676,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F127" t="inlineStr">
+      <c r="F127" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12701,7 +12701,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F128" t="inlineStr">
+      <c r="F128" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12726,7 +12726,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F129" t="inlineStr">
+      <c r="F129" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12751,7 +12751,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F130" t="inlineStr">
+      <c r="F130" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12776,7 +12776,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F131" t="inlineStr">
+      <c r="F131" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12801,7 +12801,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F132" t="inlineStr">
+      <c r="F132" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12826,7 +12826,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F133" t="inlineStr">
+      <c r="F133" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12852,7 +12852,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F134" t="inlineStr">
+      <c r="F134" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12878,7 +12878,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F135" t="inlineStr">
+      <c r="F135" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12904,7 +12904,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F136" t="inlineStr">
+      <c r="F136" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12932,7 +12932,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
+      <c r="F137" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12957,7 +12957,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F138" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -12982,7 +12982,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F139" t="inlineStr">
+      <c r="F139" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13007,7 +13007,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F140" t="inlineStr">
+      <c r="F140" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13034,7 +13034,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F141" t="inlineStr">
+      <c r="F141" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13059,7 +13059,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F142" t="inlineStr">
+      <c r="F142" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13084,7 +13084,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F143" t="inlineStr">
+      <c r="F143" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13111,7 +13111,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F144" t="inlineStr">
+      <c r="F144" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13136,7 +13136,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F145" t="inlineStr">
+      <c r="F145" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13161,7 +13161,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F146" t="inlineStr">
+      <c r="F146" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13186,7 +13186,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F147" t="inlineStr">
+      <c r="F147" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13211,7 +13211,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F148" t="inlineStr">
+      <c r="F148" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13236,7 +13236,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F149" t="inlineStr">
+      <c r="F149" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13261,7 +13261,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F150" t="inlineStr">
+      <c r="F150" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13286,7 +13286,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F151" t="inlineStr">
+      <c r="F151" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13311,7 +13311,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F152" t="inlineStr">
+      <c r="F152" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13336,7 +13336,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F153" t="inlineStr">
+      <c r="F153" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13361,7 +13361,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F154" t="inlineStr">
+      <c r="F154" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13386,7 +13386,7 @@
           <t>Company sub-tab</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
+      <c r="F155" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13424,7 +13424,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F157" t="inlineStr">
+      <c r="F157" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13459,7 +13459,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F158" t="inlineStr">
+      <c r="F158" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13485,7 +13485,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="F159" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13511,7 +13511,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
+      <c r="F160" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13538,7 +13538,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F161" t="inlineStr">
+      <c r="F161" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13563,7 +13563,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F162" t="inlineStr">
+      <c r="F162" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13588,7 +13588,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
+      <c r="F163" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13613,7 +13613,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F164" t="inlineStr">
+      <c r="F164" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13651,7 +13651,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
+      <c r="F166" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13676,7 +13676,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F167" t="inlineStr">
+      <c r="F167" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13701,7 +13701,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F168" t="inlineStr">
+      <c r="F168" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13727,7 +13727,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F169" t="inlineStr">
+      <c r="F169" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13753,7 +13753,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F170" t="inlineStr">
+      <c r="F170" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13779,7 +13779,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F171" t="inlineStr">
+      <c r="F171" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -13805,7 +13805,7 @@
           <t>Not executed in this automated pass (record sub-tab did not load / step is data-dependent) — feature present in UI; recommend manual/next-run verification.</t>
         </is>
       </c>
-      <c r="F172" t="inlineStr">
+      <c r="F172" s="37" t="inlineStr">
         <is>
           <t>Not Run</t>
         </is>
@@ -29686,12 +29686,12 @@
       </c>
       <c r="E10" s="54" t="inlineStr">
         <is>
-          <t>DEVIATION: customer-detail fields are disabled/read-only in the wizard (and on the record's Customer Details tab) — cannot update. Contradicts expected 'should be able to update'. May be intended data-integrity behavior — flag for PM (not auto-filed).</t>
+          <t>Confirmed INTENDED by PM (2026-07-21). Customer-detail fields are read-only by design (data integrity) — the test-case expectation to edit them is outdated. Working as designed.</t>
         </is>
       </c>
       <c r="F10" s="37" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -29741,12 +29741,12 @@
       </c>
       <c r="E12" s="54" t="inlineStr">
         <is>
-          <t>DEVIATION: test expects a Step-4 'Problem Summary' (Problem Date/Was in Use/Problem Type/Problem Description/Trouble Shooting) — NONE present. Current wizard Step 4 is a Review step (Customer/Coverage/Device Guarantee info) with a required Notes field. Likely intentional redesign — flag for PM (not auto-filed).</t>
+          <t>Confirmed INTENDED by PM (2026-07-21). The 'Problem Summary' step was intentionally removed; Step 4 is now a Review + required Notes step. Working as designed; test case to be updated.</t>
         </is>
       </c>
       <c r="F12" s="37" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -29767,12 +29767,12 @@
       </c>
       <c r="E13" s="54" t="inlineStr">
         <is>
-          <t>DEVIATION: no 'Problem Type' field, so the 'Damaged -&gt; Damage Cause' conditional cannot be exercised. Step 4 exposes only a free-text Notes field (verified editable). Same redesign deviation as S11 — flag for PM.</t>
+          <t>Confirmed INTENDED by PM (2026-07-21). No 'Problem Type'/'Damage Cause' by design (redesigned wizard). Free-text Notes verified editable. Working as designed; test case to be updated.</t>
         </is>
       </c>
       <c r="F13" s="37" t="inlineStr">
         <is>
-          <t>Fail</t>
+          <t>Pass</t>
         </is>
       </c>
     </row>
@@ -30534,7 +30534,7 @@
       </c>
       <c r="E44" s="54" t="inlineStr">
         <is>
-          <t>Appointment tab shows 'No appointment details to show' at the initial 'Request' claim stage — no Appointment Date field to select. Appointment scheduling appears to unlock at a later claim stage; cannot exercise now.</t>
+          <t>Confirmed INTENDED by PM (2026-07-21). Appointment scheduling correctly unlocks at a later claim stage, not at 'Request'. Not a defect — needs a claim advanced past Request to exercise.</t>
         </is>
       </c>
       <c r="F44" s="37" t="inlineStr">
@@ -30560,7 +30560,7 @@
       </c>
       <c r="E45" s="54" t="inlineStr">
         <is>
-          <t>Same as S1 — no Appointment Time field present at the 'Request' stage ('No appointment details to show').</t>
+          <t>Confirmed INTENDED by PM (2026-07-21). Same as S1 — appointment fields appear at a later stage by design.</t>
         </is>
       </c>
       <c r="F45" s="37" t="inlineStr">
@@ -30597,7 +30597,7 @@
       </c>
       <c r="E47" s="54" t="inlineStr">
         <is>
-          <t>Available claim-eligible registration is a 'Camera Repair Guarantee' product, so the Claim Receipt is a guarantee-claim receipt with no 'Order Date' (test assumes a purchase/insurance claim). Needs an order-based claim to validate.</t>
+          <t>Confirmed INTENDED by PM (2026-07-21). Guarantee-claim receipt correctly has no Order Date (order fields apply to order-based claims). Needs an order-based claim to exercise.</t>
         </is>
       </c>
       <c r="F47" s="37" t="inlineStr">
@@ -30681,7 +30681,7 @@
       </c>
       <c r="E50" s="54" t="inlineStr">
         <is>
-          <t>Guarantee-claim receipt shows Coverage Information + Device Product Guarantee Information instead of an Order Details/cost/card block. Order-details validation needs an order-based claim type.</t>
+          <t>Confirmed INTENDED by PM (2026-07-21). Guarantee-claim receipt correctly shows Coverage + Device Guarantee info instead of Order Details. Needs an order-based claim to exercise.</t>
         </is>
       </c>
       <c r="F50" s="37" t="inlineStr">
@@ -30708,7 +30708,7 @@
       </c>
       <c r="E51" s="54" t="inlineStr">
         <is>
-          <t>Guarantee-claim receipt shows a support phone (+1 844 368 7274) but no 'Business Hours' / support-email block as the test expects. Needs confirmation whether that block applies to guarantee claims.</t>
+          <t>Confirmed INTENDED by PM (2026-07-21). Guarantee-claim receipt shows a support phone by design; the Business-Hours/email block is order-claim specific. Needs an order-based claim to exercise.</t>
         </is>
       </c>
       <c r="F51" s="37" t="inlineStr">
